--- a/ktb_arb/국채선물_차익거래_간소.xlsx
+++ b/ktb_arb/국채선물_차익거래_간소.xlsx
@@ -20,8 +20,8 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0.00000000"/>
   </numFmts>
@@ -167,28 +167,28 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -199,7 +199,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -719,7 +719,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>조달금리 (레포)</t>
+          <t>조달금리 — 현물매수 시 지급</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -730,16 +730,30 @@
           <t>%</t>
         </is>
       </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>레포(RP) 조달금리. 선물매도+현물매수 방향에서 적용</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>조달금리 (소수)</t>
-        </is>
-      </c>
-      <c r="B13" s="13">
-        <f>B12/100</f>
-        <v/>
+          <t>담보운용금리 — 현물매도 시 수취</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>역RP 운용금리. 선물매수+현물매도 방향에서 적용</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -768,7 +782,7 @@
           <t>표준물 표면금리</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="13" t="n">
         <v>0.05</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -818,7 +832,7 @@
           <t>포지션 방향</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>선물매도+현물매수</t>
         </is>
@@ -835,7 +849,7 @@
           <t>방향계수</t>
         </is>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="15">
         <f>IF(B18="선물매도+현물매수",1,-1)</f>
         <v/>
       </c>
@@ -846,7 +860,7 @@
           <t>선물 진입가</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n"/>
+      <c r="B20" s="16" t="n"/>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>빈칸이면 현재가 사용</t>
@@ -859,7 +873,7 @@
           <t>▶ 적용 진입가</t>
         </is>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <f>IF(B20="",B25,B20)</f>
         <v/>
       </c>
@@ -881,6 +895,27 @@
       <c r="F22" s="7" t="inlineStr">
         <is>
           <t>선물수수료 + 채권 스프레드 + 슬리피지</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>▶ 적용금리 (방향 반영)</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
+        <f>IF($B$19=1,$B$12,$B$13)</f>
+        <v/>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>캐리 계산과 쿠폰 재투자에 모두 이 금리를 쓴다</t>
         </is>
       </c>
     </row>
@@ -915,7 +950,7 @@
           <t>선물 종목코드</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>A6769000</t>
         </is>
@@ -1034,12 +1069,12 @@
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>KR103502GE97</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>KR103503GG60</t>
         </is>
@@ -1052,12 +1087,12 @@
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>국고 25-5</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>국고 25-11</t>
         </is>
@@ -1164,11 +1199,11 @@
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr"/>
-      <c r="C41" s="13">
+      <c r="C41" s="24">
         <f>C40/100</f>
         <v/>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="24">
         <f>D40/100</f>
         <v/>
       </c>
@@ -1217,11 +1252,11 @@
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr"/>
-      <c r="C44" s="24">
+      <c r="C44" s="18">
         <f>엔진!$B$84</f>
         <v/>
       </c>
-      <c r="D44" s="24">
+      <c r="D44" s="18">
         <f>엔진!$AF$84</f>
         <v/>
       </c>
@@ -1305,11 +1340,11 @@
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr"/>
-      <c r="C49" s="24">
+      <c r="C49" s="18">
         <f>엔진!$B$98</f>
         <v/>
       </c>
-      <c r="D49" s="24">
+      <c r="D49" s="18">
         <f>엔진!$AF$98</f>
         <v/>
       </c>
@@ -1330,11 +1365,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="18">
         <f>엔진!$B$109*100</f>
         <v/>
       </c>
-      <c r="D50" s="24">
+      <c r="D50" s="18">
         <f>엔진!$AF$109*100</f>
         <v/>
       </c>
@@ -1371,11 +1406,11 @@
           <t>포인트/1bp</t>
         </is>
       </c>
-      <c r="C52" s="13">
+      <c r="C52" s="24">
         <f>엔진!$B$108</f>
         <v/>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="24">
         <f>엔진!$AF$108</f>
         <v/>
       </c>
@@ -1460,11 +1495,11 @@
           <t>원</t>
         </is>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="15">
         <f>C55*$B$17</f>
         <v/>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="15">
         <f>D55*$B$17</f>
         <v/>
       </c>
@@ -1551,7 +1586,7 @@
           <t xml:space="preserve">  P(ȳ+1bp)</t>
         </is>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="24">
         <f>($B$15*100/($B$65+0.0001))*(1-(1/(1+($B$65+0.0001)/2))^($B$14*2))+100*(1/(1+($B$65+0.0001)/2))^($B$14*2)</f>
         <v/>
       </c>
@@ -1562,7 +1597,7 @@
           <t xml:space="preserve">  P(ȳ−1bp)</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="24">
         <f>($B$15*100/($B$65-0.0001))*(1-(1/(1+($B$65-0.0001)/2))^($B$14*2))+100*(1/(1+($B$65-0.0001)/2))^($B$14*2)</f>
         <v/>
       </c>
@@ -1589,7 +1624,7 @@
           <t>바스켓 평균 선도수익률</t>
         </is>
       </c>
-      <c r="B64" s="24">
+      <c r="B64" s="18">
         <f>SUMPRODUCT(C50:D50,C39:D39)/SUM(C39:D39)</f>
         <v/>
       </c>
@@ -1616,7 +1651,7 @@
           <t>▶ 이론 선물가격</t>
         </is>
       </c>
-      <c r="B66" s="24">
+      <c r="B66" s="18">
         <f>($B$15*100/($B$65))*(1-(1/(1+($B$65)/2))^($B$14*2))+100*(1/(1+($B$65)/2))^($B$14*2)</f>
         <v/>
       </c>
@@ -1643,7 +1678,7 @@
           <t>▶ 베이시스</t>
         </is>
       </c>
-      <c r="B68" s="24">
+      <c r="B68" s="18">
         <f>B67-B66</f>
         <v/>
       </c>
@@ -1675,7 +1710,7 @@
           <t>총 거래비용</t>
         </is>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="15">
         <f>$B$22</f>
         <v/>
       </c>
@@ -1777,7 +1812,7 @@
           <t>[참고] 위 둘의 차이 = 캐리</t>
         </is>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="15">
         <f>(B77-B66)*$B$16</f>
         <v/>
       </c>
@@ -1839,7 +1874,7 @@
           <t>만기 수익률 shift</t>
         </is>
       </c>
-      <c r="B83" s="17" t="n">
+      <c r="B83" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -1875,7 +1910,7 @@
           <t>▶ 최종결제기준가격</t>
         </is>
       </c>
-      <c r="B85" s="24">
+      <c r="B85" s="18">
         <f>($B$15*100/($B$84/100))*(1-(1/(1+($B$84/100)/2))^($B$14*2))+100*(1/(1+($B$84/100)/2))^($B$14*2)</f>
         <v/>
       </c>
@@ -1886,7 +1921,7 @@
           <t>선물 leg</t>
         </is>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="15">
         <f>($B$21-B85)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
@@ -1902,7 +1937,7 @@
           <t>현물 leg</t>
         </is>
       </c>
-      <c r="B87" s="16">
+      <c r="B87" s="15">
         <f>$B$19*((엔진!$B$114-C49)/100*C58+(엔진!$AF$114-D49)/100*D58)</f>
         <v/>
       </c>
@@ -1918,7 +1953,7 @@
           <t>거래비용</t>
         </is>
       </c>
-      <c r="B88" s="16">
+      <c r="B88" s="15">
         <f>-$B$22*$B$17</f>
         <v/>
       </c>
@@ -1966,7 +2001,7 @@
           <t>바스켓 투자금액</t>
         </is>
       </c>
-      <c r="B91" s="16">
+      <c r="B91" s="15">
         <f>SUMPRODUCT(C44:D44,C58:D58)/100</f>
         <v/>
       </c>
@@ -2055,19 +2090,19 @@
         <f>($B$15*100/($B96/100))*(1-(1/(1+($B96/100)/2))^($B$14*2))+100*(1/(1+($B96/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="15">
         <f>($B$21-$C96)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E96" s="16">
+      <c r="E96" s="15">
         <f>$B$19*((엔진!$B$115-$C$49)/100*$C$58+(엔진!$AF$115-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F96" s="16">
+      <c r="F96" s="15">
         <f>$D96+$E96-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G96" s="16">
+      <c r="G96" s="15">
         <f>IFERROR($F96/$B$17,0)</f>
         <v/>
       </c>
@@ -2084,19 +2119,19 @@
         <f>($B$15*100/($B97/100))*(1-(1/(1+($B97/100)/2))^($B$14*2))+100*(1/(1+($B97/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D97" s="16">
+      <c r="D97" s="15">
         <f>($B$21-$C97)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E97" s="16">
+      <c r="E97" s="15">
         <f>$B$19*((엔진!$B$116-$C$49)/100*$C$58+(엔진!$AF$116-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F97" s="16">
+      <c r="F97" s="15">
         <f>$D97+$E97-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G97" s="16">
+      <c r="G97" s="15">
         <f>IFERROR($F97/$B$17,0)</f>
         <v/>
       </c>
@@ -2113,19 +2148,19 @@
         <f>($B$15*100/($B98/100))*(1-(1/(1+($B98/100)/2))^($B$14*2))+100*(1/(1+($B98/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D98" s="16">
+      <c r="D98" s="15">
         <f>($B$21-$C98)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E98" s="16">
+      <c r="E98" s="15">
         <f>$B$19*((엔진!$B$117-$C$49)/100*$C$58+(엔진!$AF$117-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F98" s="16">
+      <c r="F98" s="15">
         <f>$D98+$E98-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G98" s="16">
+      <c r="G98" s="15">
         <f>IFERROR($F98/$B$17,0)</f>
         <v/>
       </c>
@@ -2142,19 +2177,19 @@
         <f>($B$15*100/($B99/100))*(1-(1/(1+($B99/100)/2))^($B$14*2))+100*(1/(1+($B99/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D99" s="16">
+      <c r="D99" s="15">
         <f>($B$21-$C99)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E99" s="16">
+      <c r="E99" s="15">
         <f>$B$19*((엔진!$B$118-$C$49)/100*$C$58+(엔진!$AF$118-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F99" s="16">
+      <c r="F99" s="15">
         <f>$D99+$E99-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G99" s="16">
+      <c r="G99" s="15">
         <f>IFERROR($F99/$B$17,0)</f>
         <v/>
       </c>
@@ -2200,19 +2235,19 @@
         <f>($B$15*100/($B101/100))*(1-(1/(1+($B101/100)/2))^($B$14*2))+100*(1/(1+($B101/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="15">
         <f>($B$21-$C101)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="15">
         <f>$B$19*((엔진!$B$120-$C$49)/100*$C$58+(엔진!$AF$120-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F101" s="16">
+      <c r="F101" s="15">
         <f>$D101+$E101-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G101" s="16">
+      <c r="G101" s="15">
         <f>IFERROR($F101/$B$17,0)</f>
         <v/>
       </c>
@@ -2229,19 +2264,19 @@
         <f>($B$15*100/($B102/100))*(1-(1/(1+($B102/100)/2))^($B$14*2))+100*(1/(1+($B102/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D102" s="16">
+      <c r="D102" s="15">
         <f>($B$21-$C102)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E102" s="16">
+      <c r="E102" s="15">
         <f>$B$19*((엔진!$B$121-$C$49)/100*$C$58+(엔진!$AF$121-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F102" s="16">
+      <c r="F102" s="15">
         <f>$D102+$E102-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G102" s="16">
+      <c r="G102" s="15">
         <f>IFERROR($F102/$B$17,0)</f>
         <v/>
       </c>
@@ -2258,19 +2293,19 @@
         <f>($B$15*100/($B103/100))*(1-(1/(1+($B103/100)/2))^($B$14*2))+100*(1/(1+($B103/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D103" s="16">
+      <c r="D103" s="15">
         <f>($B$21-$C103)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E103" s="16">
+      <c r="E103" s="15">
         <f>$B$19*((엔진!$B$122-$C$49)/100*$C$58+(엔진!$AF$122-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F103" s="16">
+      <c r="F103" s="15">
         <f>$D103+$E103-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G103" s="16">
+      <c r="G103" s="15">
         <f>IFERROR($F103/$B$17,0)</f>
         <v/>
       </c>
@@ -2287,19 +2322,19 @@
         <f>($B$15*100/($B104/100))*(1-(1/(1+($B104/100)/2))^($B$14*2))+100*(1/(1+($B104/100)/2))^($B$14*2)</f>
         <v/>
       </c>
-      <c r="D104" s="16">
+      <c r="D104" s="15">
         <f>($B$21-$C104)*$B$19*$B$16*$B$17</f>
         <v/>
       </c>
-      <c r="E104" s="16">
+      <c r="E104" s="15">
         <f>$B$19*((엔진!$B$123-$C$49)/100*$C$58+(엔진!$AF$123-$D$49)/100*$D$58)</f>
         <v/>
       </c>
-      <c r="F104" s="16">
+      <c r="F104" s="15">
         <f>$D104+$E104-$B$22*$B$17</f>
         <v/>
       </c>
-      <c r="G104" s="16">
+      <c r="G104" s="15">
         <f>IFERROR($F104/$B$17,0)</f>
         <v/>
       </c>
@@ -2506,7 +2541,7 @@
           <t>표면금리(소수)</t>
         </is>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="24">
         <f>메인!C36/100</f>
         <v/>
       </c>
@@ -2515,7 +2550,7 @@
           <t>표면금리(소수)</t>
         </is>
       </c>
-      <c r="AF4" s="13">
+      <c r="AF4" s="24">
         <f>메인!D36/100</f>
         <v/>
       </c>
@@ -2526,7 +2561,7 @@
           <t>반기쿠폰</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="24">
         <f>B4*100/2</f>
         <v/>
       </c>
@@ -2535,7 +2570,7 @@
           <t>반기쿠폰</t>
         </is>
       </c>
-      <c r="AF5" s="13">
+      <c r="AF5" s="24">
         <f>AF4*100/2</f>
         <v/>
       </c>
@@ -2586,7 +2621,7 @@
           <t>현물수익률(소수)</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="24">
         <f>메인!C41</f>
         <v/>
       </c>
@@ -2595,7 +2630,7 @@
           <t>현물수익률(소수)</t>
         </is>
       </c>
-      <c r="AF8" s="13">
+      <c r="AF8" s="24">
         <f>메인!D41</f>
         <v/>
       </c>
@@ -2603,20 +2638,20 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>조달금리(소수)</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>메인!$B$13</f>
+          <t>적용금리(소수)</t>
+        </is>
+      </c>
+      <c r="B9" s="24">
+        <f>메인!$B$23/100</f>
         <v/>
       </c>
       <c r="AE9" s="5" t="inlineStr">
         <is>
-          <t>조달금리(소수)</t>
-        </is>
-      </c>
-      <c r="AF9" s="13">
-        <f>메인!$B$13</f>
+          <t>적용금리(소수)</t>
+        </is>
+      </c>
+      <c r="AF9" s="24">
+        <f>메인!$B$23/100</f>
         <v/>
       </c>
     </row>
@@ -2626,7 +2661,7 @@
           <t>손익 shift(bp)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="24">
         <f>메인!$B$83</f>
         <v/>
       </c>
@@ -2635,7 +2670,7 @@
           <t>손익 shift(bp)</t>
         </is>
       </c>
-      <c r="AF10" s="13">
+      <c r="AF10" s="24">
         <f>메인!$B$83</f>
         <v/>
       </c>
@@ -16840,7 +16875,7 @@
           <t>잔존 이표횟수</t>
         </is>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="15">
         <f>SUM(D15:D76)</f>
         <v/>
       </c>
@@ -16849,7 +16884,7 @@
           <t>잔존 이표횟수</t>
         </is>
       </c>
-      <c r="AF79" s="16">
+      <c r="AF79" s="15">
         <f>SUM(AH15:AH76)</f>
         <v/>
       </c>
@@ -16900,7 +16935,7 @@
           <t>d</t>
         </is>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="15">
         <f>B80-B6</f>
         <v/>
       </c>
@@ -16909,7 +16944,7 @@
           <t>d</t>
         </is>
       </c>
-      <c r="AF82" s="16">
+      <c r="AF82" s="15">
         <f>AF80-AF6</f>
         <v/>
       </c>
@@ -16920,7 +16955,7 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="15">
         <f>B80-B81</f>
         <v/>
       </c>
@@ -16929,7 +16964,7 @@
           <t>T</t>
         </is>
       </c>
-      <c r="AF83" s="16">
+      <c r="AF83" s="15">
         <f>AF80-AF81</f>
         <v/>
       </c>
@@ -16940,7 +16975,7 @@
           <t>현물단가(더티)</t>
         </is>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="24">
         <f>SUM(F15:F76)/(1+B8/2*B82/B83)</f>
         <v/>
       </c>
@@ -16949,7 +16984,7 @@
           <t>현물단가(더티)</t>
         </is>
       </c>
-      <c r="AF84" s="13">
+      <c r="AF84" s="24">
         <f>SUM(AJ15:AJ76)/(1+AF8/2*AF82/AF83)</f>
         <v/>
       </c>
@@ -16960,7 +16995,7 @@
           <t>P0 @+1bp</t>
         </is>
       </c>
-      <c r="B85" s="13">
+      <c r="B85" s="24">
         <f>SUM(G15:G76)/(1+(B8+0.0001)/2*B82/B83)</f>
         <v/>
       </c>
@@ -16969,7 +17004,7 @@
           <t>P0 @+1bp</t>
         </is>
       </c>
-      <c r="AF85" s="13">
+      <c r="AF85" s="24">
         <f>SUM(AK15:AK76)/(1+(AF8+0.0001)/2*AF82/AF83)</f>
         <v/>
       </c>
@@ -16980,7 +17015,7 @@
           <t>P0 @−1bp</t>
         </is>
       </c>
-      <c r="B86" s="13">
+      <c r="B86" s="24">
         <f>SUM(H15:H76)/(1+(B8-0.0001)/2*B82/B83)</f>
         <v/>
       </c>
@@ -16989,7 +17024,7 @@
           <t>P0 @−1bp</t>
         </is>
       </c>
-      <c r="AF86" s="13">
+      <c r="AF86" s="24">
         <f>SUM(AL15:AL76)/(1+(AF8-0.0001)/2*AF82/AF83)</f>
         <v/>
       </c>
@@ -17000,7 +17035,7 @@
           <t>현물 BPV</t>
         </is>
       </c>
-      <c r="B87" s="13">
+      <c r="B87" s="24">
         <f>(B86-B85)/2</f>
         <v/>
       </c>
@@ -17009,7 +17044,7 @@
           <t>현물 BPV</t>
         </is>
       </c>
-      <c r="AF87" s="13">
+      <c r="AF87" s="24">
         <f>(AF86-AF85)/2</f>
         <v/>
       </c>
@@ -17092,7 +17127,7 @@
           <t>d_H</t>
         </is>
       </c>
-      <c r="B93" s="16">
+      <c r="B93" s="15">
         <f>B91-B7</f>
         <v/>
       </c>
@@ -17101,7 +17136,7 @@
           <t>d_H</t>
         </is>
       </c>
-      <c r="AF93" s="16">
+      <c r="AF93" s="15">
         <f>AF91-AF7</f>
         <v/>
       </c>
@@ -17112,7 +17147,7 @@
           <t>T_H</t>
         </is>
       </c>
-      <c r="B94" s="16">
+      <c r="B94" s="15">
         <f>B91-B92</f>
         <v/>
       </c>
@@ -17121,7 +17156,7 @@
           <t>T_H</t>
         </is>
       </c>
-      <c r="AF94" s="16">
+      <c r="AF94" s="15">
         <f>AF91-AF92</f>
         <v/>
       </c>
@@ -17132,7 +17167,7 @@
           <t>쿠폰 재투자FV</t>
         </is>
       </c>
-      <c r="B95" s="13">
+      <c r="B95" s="24">
         <f>SUM(R15:R76)</f>
         <v/>
       </c>
@@ -17141,7 +17176,7 @@
           <t>쿠폰 재투자FV</t>
         </is>
       </c>
-      <c r="AF95" s="13">
+      <c r="AF95" s="24">
         <f>SUM(AV15:AV76)</f>
         <v/>
       </c>
@@ -17152,7 +17187,7 @@
           <t>조달일수</t>
         </is>
       </c>
-      <c r="B96" s="16">
+      <c r="B96" s="15">
         <f>B7-B6</f>
         <v/>
       </c>
@@ -17161,7 +17196,7 @@
           <t>조달일수</t>
         </is>
       </c>
-      <c r="AF96" s="16">
+      <c r="AF96" s="15">
         <f>AF7-AF6</f>
         <v/>
       </c>
@@ -17172,7 +17207,7 @@
           <t>조달이자</t>
         </is>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="24">
         <f>B84*B9*B96/365</f>
         <v/>
       </c>
@@ -17181,7 +17216,7 @@
           <t>조달이자</t>
         </is>
       </c>
-      <c r="AF97" s="13">
+      <c r="AF97" s="24">
         <f>AF84*AF9*AF96/365</f>
         <v/>
       </c>
@@ -17192,7 +17227,7 @@
           <t>선도 목표단가</t>
         </is>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="24">
         <f>B84+B97-B95</f>
         <v/>
       </c>
@@ -17201,7 +17236,7 @@
           <t>선도 목표단가</t>
         </is>
       </c>
-      <c r="AF98" s="13">
+      <c r="AF98" s="24">
         <f>AF84+AF97-AF95</f>
         <v/>
       </c>
@@ -17232,7 +17267,7 @@
           <t>P_H(y0)</t>
         </is>
       </c>
-      <c r="B100" s="13">
+      <c r="B100" s="24">
         <f>SUM(K15:K76)/(1+B99/2*B93/B94)</f>
         <v/>
       </c>
@@ -17241,7 +17276,7 @@
           <t>P_H(y0)</t>
         </is>
       </c>
-      <c r="AF100" s="13">
+      <c r="AF100" s="24">
         <f>SUM(AO15:AO76)/(1+AF99/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17252,7 +17287,7 @@
           <t>P_H(y0+1bp)</t>
         </is>
       </c>
-      <c r="B101" s="13">
+      <c r="B101" s="24">
         <f>SUM(L15:L76)/(1+(B99+0.0001)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17261,7 +17296,7 @@
           <t>P_H(y0+1bp)</t>
         </is>
       </c>
-      <c r="AF101" s="13">
+      <c r="AF101" s="24">
         <f>SUM(AP15:AP76)/(1+(AF99+0.0001)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17272,7 +17307,7 @@
           <t>P_H(y0−1bp)</t>
         </is>
       </c>
-      <c r="B102" s="13">
+      <c r="B102" s="24">
         <f>SUM(M15:M76)/(1+(B99-0.0001)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17281,7 +17316,7 @@
           <t>P_H(y0−1bp)</t>
         </is>
       </c>
-      <c r="AF102" s="13">
+      <c r="AF102" s="24">
         <f>SUM(AQ15:AQ76)/(1+(AF99-0.0001)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17292,7 +17327,7 @@
           <t>|dP/dy|</t>
         </is>
       </c>
-      <c r="B103" s="13">
+      <c r="B103" s="24">
         <f>(B102-B101)/0.0002</f>
         <v/>
       </c>
@@ -17301,7 +17336,7 @@
           <t>|dP/dy|</t>
         </is>
       </c>
-      <c r="AF103" s="13">
+      <c r="AF103" s="24">
         <f>(AF102-AF101)/0.0002</f>
         <v/>
       </c>
@@ -17332,7 +17367,7 @@
           <t>P_H(y1)</t>
         </is>
       </c>
-      <c r="B105" s="13">
+      <c r="B105" s="24">
         <f>SUM(N15:N76)/(1+B104/2*B93/B94)</f>
         <v/>
       </c>
@@ -17341,7 +17376,7 @@
           <t>P_H(y1)</t>
         </is>
       </c>
-      <c r="AF105" s="13">
+      <c r="AF105" s="24">
         <f>SUM(AR15:AR76)/(1+AF104/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17352,7 +17387,7 @@
           <t>P_H(y1+1bp)</t>
         </is>
       </c>
-      <c r="B106" s="13">
+      <c r="B106" s="24">
         <f>SUM(O15:O76)/(1+(B104+0.0001)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17361,7 +17396,7 @@
           <t>P_H(y1+1bp)</t>
         </is>
       </c>
-      <c r="AF106" s="13">
+      <c r="AF106" s="24">
         <f>SUM(AS15:AS76)/(1+(AF104+0.0001)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17372,7 +17407,7 @@
           <t>P_H(y1−1bp)</t>
         </is>
       </c>
-      <c r="B107" s="13">
+      <c r="B107" s="24">
         <f>SUM(P15:P76)/(1+(B104-0.0001)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17381,7 +17416,7 @@
           <t>P_H(y1−1bp)</t>
         </is>
       </c>
-      <c r="AF107" s="13">
+      <c r="AF107" s="24">
         <f>SUM(AT15:AT76)/(1+(AF104-0.0001)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17392,7 +17427,7 @@
           <t>▶ 선도 BPV</t>
         </is>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="24">
         <f>(B107-B106)/2</f>
         <v/>
       </c>
@@ -17401,7 +17436,7 @@
           <t>▶ 선도 BPV</t>
         </is>
       </c>
-      <c r="AF108" s="13">
+      <c r="AF108" s="24">
         <f>(AF107-AF106)/2</f>
         <v/>
       </c>
@@ -17432,7 +17467,7 @@
           <t>P_H(y2)</t>
         </is>
       </c>
-      <c r="B110" s="13">
+      <c r="B110" s="24">
         <f>SUM(Q15:Q76)/(1+B109/2*B93/B94)</f>
         <v/>
       </c>
@@ -17441,7 +17476,7 @@
           <t>P_H(y2)</t>
         </is>
       </c>
-      <c r="AF110" s="13">
+      <c r="AF110" s="24">
         <f>SUM(AU15:AU76)/(1+AF109/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17484,7 +17519,7 @@
           <t>만기단가 — 손익 shift</t>
         </is>
       </c>
-      <c r="B114" s="13">
+      <c r="B114" s="24">
         <f>SUM(S15:S76)/(1+(B109+$B$10/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17493,7 +17528,7 @@
           <t>만기단가 — 손익 shift</t>
         </is>
       </c>
-      <c r="AF114" s="13">
+      <c r="AF114" s="24">
         <f>SUM(AW15:AW76)/(1+(AF109+$AF$10/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17504,7 +17539,7 @@
           <t>만기단가 — 시나리오 -100bp</t>
         </is>
       </c>
-      <c r="B115" s="13">
+      <c r="B115" s="24">
         <f>SUM(T15:T76)/(1+(B109+메인!$A$96/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17513,7 +17548,7 @@
           <t>만기단가 — 시나리오 -100bp</t>
         </is>
       </c>
-      <c r="AF115" s="13">
+      <c r="AF115" s="24">
         <f>SUM(AX15:AX76)/(1+(AF109+메인!$A$96/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17524,7 +17559,7 @@
           <t>만기단가 — 시나리오 -75bp</t>
         </is>
       </c>
-      <c r="B116" s="13">
+      <c r="B116" s="24">
         <f>SUM(U15:U76)/(1+(B109+메인!$A$97/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17533,7 +17568,7 @@
           <t>만기단가 — 시나리오 -75bp</t>
         </is>
       </c>
-      <c r="AF116" s="13">
+      <c r="AF116" s="24">
         <f>SUM(AY15:AY76)/(1+(AF109+메인!$A$97/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17544,7 +17579,7 @@
           <t>만기단가 — 시나리오 -50bp</t>
         </is>
       </c>
-      <c r="B117" s="13">
+      <c r="B117" s="24">
         <f>SUM(V15:V76)/(1+(B109+메인!$A$98/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17553,7 +17588,7 @@
           <t>만기단가 — 시나리오 -50bp</t>
         </is>
       </c>
-      <c r="AF117" s="13">
+      <c r="AF117" s="24">
         <f>SUM(AZ15:AZ76)/(1+(AF109+메인!$A$98/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17564,7 +17599,7 @@
           <t>만기단가 — 시나리오 -25bp</t>
         </is>
       </c>
-      <c r="B118" s="13">
+      <c r="B118" s="24">
         <f>SUM(W15:W76)/(1+(B109+메인!$A$99/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17573,7 +17608,7 @@
           <t>만기단가 — 시나리오 -25bp</t>
         </is>
       </c>
-      <c r="AF118" s="13">
+      <c r="AF118" s="24">
         <f>SUM(BA15:BA76)/(1+(AF109+메인!$A$99/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17584,7 +17619,7 @@
           <t>만기단가 — 시나리오 +0bp</t>
         </is>
       </c>
-      <c r="B119" s="13">
+      <c r="B119" s="24">
         <f>SUM(X15:X76)/(1+(B109+메인!$A$100/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17593,7 +17628,7 @@
           <t>만기단가 — 시나리오 +0bp</t>
         </is>
       </c>
-      <c r="AF119" s="13">
+      <c r="AF119" s="24">
         <f>SUM(BB15:BB76)/(1+(AF109+메인!$A$100/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17604,7 +17639,7 @@
           <t>만기단가 — 시나리오 +25bp</t>
         </is>
       </c>
-      <c r="B120" s="13">
+      <c r="B120" s="24">
         <f>SUM(Y15:Y76)/(1+(B109+메인!$A$101/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17613,7 +17648,7 @@
           <t>만기단가 — 시나리오 +25bp</t>
         </is>
       </c>
-      <c r="AF120" s="13">
+      <c r="AF120" s="24">
         <f>SUM(BC15:BC76)/(1+(AF109+메인!$A$101/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17624,7 +17659,7 @@
           <t>만기단가 — 시나리오 +50bp</t>
         </is>
       </c>
-      <c r="B121" s="13">
+      <c r="B121" s="24">
         <f>SUM(Z15:Z76)/(1+(B109+메인!$A$102/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17633,7 +17668,7 @@
           <t>만기단가 — 시나리오 +50bp</t>
         </is>
       </c>
-      <c r="AF121" s="13">
+      <c r="AF121" s="24">
         <f>SUM(BD15:BD76)/(1+(AF109+메인!$A$102/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17644,7 +17679,7 @@
           <t>만기단가 — 시나리오 +75bp</t>
         </is>
       </c>
-      <c r="B122" s="13">
+      <c r="B122" s="24">
         <f>SUM(AA15:AA76)/(1+(B109+메인!$A$103/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17653,7 +17688,7 @@
           <t>만기단가 — 시나리오 +75bp</t>
         </is>
       </c>
-      <c r="AF122" s="13">
+      <c r="AF122" s="24">
         <f>SUM(BE15:BE76)/(1+(AF109+메인!$A$103/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
@@ -17664,7 +17699,7 @@
           <t>만기단가 — 시나리오 +100bp</t>
         </is>
       </c>
-      <c r="B123" s="13">
+      <c r="B123" s="24">
         <f>SUM(AB15:AB76)/(1+(B109+메인!$A$104/10000)/2*B93/B94)</f>
         <v/>
       </c>
@@ -17673,7 +17708,7 @@
           <t>만기단가 — 시나리오 +100bp</t>
         </is>
       </c>
-      <c r="AF123" s="13">
+      <c r="AF123" s="24">
         <f>SUM(BF15:BF76)/(1+(AF109+메인!$A$104/10000)/2*AF93/AF94)</f>
         <v/>
       </c>

--- a/ktb_arb/국채선물_차익거래_간소.xlsx
+++ b/ktb_arb/국채선물_차익거래_간소.xlsx
@@ -172,9 +172,9 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -901,21 +901,20 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>▶ 적용금리 (방향 반영)</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
-        <f>IF($B$19=1,$B$12,$B$13)</f>
-        <v/>
+          <t>대차수수료 / 조달조정</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>캐리 계산과 쿠폰 재투자에 모두 이 금리를 쓴다</t>
+          <t>현물매도 시 대차수수료(양수 입력) / 현물매수 시 special 프리미엄(양수 입력). 적용금리에서 차감</t>
         </is>
       </c>
     </row>
@@ -939,7 +938,7 @@
           <t>선물 현재가</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="18">
         <f>_xll.IMDP("FUT",$B$26,"선물호가_현재가")</f>
         <v/>
       </c>
@@ -967,7 +966,7 @@
           <t>종목1 수익률</t>
         </is>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="19">
         <f>_xll.IMDP("BND",$C$34,"장내국채-매도수익률1")</f>
         <v/>
       </c>
@@ -988,7 +987,7 @@
           <t>종목2 수익률</t>
         </is>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="19">
         <f>_xll.IMDP("BND",$D$34,"장내국채-매도수익률1")</f>
         <v/>
       </c>
@@ -1004,7 +1003,7 @@
           <t>인포맥스 이론가 (참고)</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="18">
         <f>_xll.IMDP("FUT",$B$26,"이론가")</f>
         <v/>
       </c>
@@ -1018,6 +1017,27 @@
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>※ 종목1을 실시간으로 못 받으면 B27 을  =B28-2.6/100  처럼 스프레드 파생식으로 바꾸십시오 (원본 파일 방식). 단 스프레드는 수동 갱신이 필요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>▶ 적용금리 (방향·조정 반영)</t>
+        </is>
+      </c>
+      <c r="B31" s="20">
+        <f>IF($B$19=1,$B$12,$B$13)-$B$23/100</f>
+        <v/>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>IF(방향=매수, 조달금리 B12, 담보운용금리 B13) − 대차수수료 B23 → 캐리·쿠폰 재투자에 적용</t>
         </is>
       </c>
     </row>
@@ -1183,11 +1203,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="19">
         <f>B27</f>
         <v/>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="19">
         <f>B28</f>
         <v/>
       </c>
@@ -1252,11 +1272,11 @@
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr"/>
-      <c r="C44" s="18">
+      <c r="C44" s="20">
         <f>엔진!$B$84</f>
         <v/>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="20">
         <f>엔진!$AF$84</f>
         <v/>
       </c>
@@ -1340,11 +1360,11 @@
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr"/>
-      <c r="C49" s="18">
+      <c r="C49" s="20">
         <f>엔진!$B$98</f>
         <v/>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="20">
         <f>엔진!$AF$98</f>
         <v/>
       </c>
@@ -1365,11 +1385,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="20">
         <f>엔진!$B$109*100</f>
         <v/>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="20">
         <f>엔진!$AF$109*100</f>
         <v/>
       </c>
@@ -1624,7 +1644,7 @@
           <t>바스켓 평균 선도수익률</t>
         </is>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="20">
         <f>SUMPRODUCT(C50:D50,C39:D39)/SUM(C39:D39)</f>
         <v/>
       </c>
@@ -1651,7 +1671,7 @@
           <t>▶ 이론 선물가격</t>
         </is>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="20">
         <f>($B$15*100/($B$65))*(1-(1/(1+($B$65)/2))^($B$14*2))+100*(1/(1+($B$65)/2))^($B$14*2)</f>
         <v/>
       </c>
@@ -1678,7 +1698,7 @@
           <t>▶ 베이시스</t>
         </is>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="20">
         <f>B67-B66</f>
         <v/>
       </c>
@@ -1910,7 +1930,7 @@
           <t>▶ 최종결제기준가격</t>
         </is>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="20">
         <f>($B$15*100/($B$84/100))*(1-(1/(1+($B$84/100)/2))^($B$14*2))+100*(1/(1+($B$84/100)/2))^($B$14*2)</f>
         <v/>
       </c>
@@ -2642,7 +2662,7 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>메인!$B$23/100</f>
+        <f>메인!$B$31/100</f>
         <v/>
       </c>
       <c r="AE9" s="5" t="inlineStr">
@@ -2651,7 +2671,7 @@
         </is>
       </c>
       <c r="AF9" s="24">
-        <f>메인!$B$23/100</f>
+        <f>메인!$B$31/100</f>
         <v/>
       </c>
     </row>

--- a/ktb_arb/국채선물_차익거래_간소.xlsx
+++ b/ktb_arb/국채선물_차익거래_간소.xlsx
@@ -901,7 +901,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>대차수수료 / 조달조정</t>
+          <t>대차수수료 (현물매도 시에만)</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>현물매도 시 대차수수료(양수 입력) / 현물매수 시 special 프리미엄(양수 입력). 적용금리에서 차감</t>
+          <t>현물을 빌려서 파는 방향에서만 적용. 현물매수 방향에서는 무시된다 (산 채권을 대차로 빌려주는 것은 별도 영업이며, special 이점은 조달금리 B12 에 이미 반영됨)</t>
         </is>
       </c>
     </row>
@@ -1023,11 +1023,11 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>▶ 적용금리 (방향·조정 반영)</t>
+          <t>▶ 적용금리 (방향 반영)</t>
         </is>
       </c>
       <c r="B31" s="20">
-        <f>IF($B$19=1,$B$12,$B$13)-$B$23/100</f>
+        <f>IF($B$19=1,$B$12,$B$13-$B$23/100)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>IF(방향=매수, 조달금리 B12, 담보운용금리 B13) − 대차수수료 B23 → 캐리·쿠폰 재투자에 적용</t>
+          <t>현물매수 → 조달금리 B12 그대로.  현물매도 → 담보운용금리 B13 − 대차수수료 B23</t>
         </is>
       </c>
     </row>

--- a/ktb_arb/국채선물_차익거래_간소.xlsx
+++ b/ktb_arb/국채선물_차익거래_간소.xlsx
@@ -719,7 +719,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>조달금리 — 현물매수 시 지급</t>
+          <t>조달금리 — 바스켓 매수 시 지급</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -732,14 +732,14 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>레포(RP) 조달금리. 선물매도+현물매수 방향에서 적용</t>
+          <t>레포(RP) 조달금리.  매수차익거래(바스켓매수+선물매도)에서 적용</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>담보운용금리 — 현물매도 시 수취</t>
+          <t>담보운용금리 — 바스켓 매도 시 수취</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>역RP 운용금리. 선물매수+현물매도 방향에서 적용</t>
+          <t>역RP 운용금리.  매도차익거래(바스켓매도+선물매수)에서 적용</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>선물매도+현물매수</t>
+          <t>매수차익 (바스켓매수+선물매도)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>선물매도+현물매수 / 선물매수+현물매도</t>
+          <t>매수차익 = 바스켓매수+선물매도   /   매도차익 = 바스켓매도+선물매수</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>IF(B18="선물매도+현물매수",1,-1)</f>
+        <f>IF(LEFT($B$18,4)="매수차익",1,-1)</f>
         <v/>
       </c>
     </row>
@@ -901,7 +901,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>대차수수료 (현물매도 시에만)</t>
+          <t>대차수수료 (매도차익 시에만)</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>현물을 빌려서 파는 방향에서만 적용. 현물매수 방향에서는 무시된다 (산 채권을 대차로 빌려주는 것은 별도 영업이며, special 이점은 조달금리 B12 에 이미 반영됨)</t>
+          <t>바스켓을 빌려서 파는 매도차익거래에만 적용. 매수차익거래에서는 무시된다 (산 채권을 대차로 빌려주는 것은 별도 영업이며, special 이점은 조달금리 B12 에 이미 반영됨)</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>현물매수 → 조달금리 B12 그대로.  현물매도 → 담보운용금리 B13 − 대차수수료 B23</t>
+          <t>매수차익 → 조달금리 B12 그대로.  매도차익 → 담보운용금리 B13 − 대차수수료 B23</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>IF(B68&gt;0,"선물 매도 + 바스켓 매수",IF(B68&lt;0,"선물 매수 + 바스켓 매도","중립"))</f>
+        <f>IF(B68&gt;0,"매수차익 (바스켓매수+선물매도)",IF(B68&lt;0,"매도차익 (바스켓매도+선물매수)","중립"))</f>
         <v/>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"선물매도+현물매수,선물매수+현물매도"</formula1>
+      <formula1>"매수차익 (바스켓매수+선물매도),매도차익 (바스켓매도+선물매수)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ktb_arb/국채선물_차익거래_간소.xlsx
+++ b/ktb_arb/국채선물_차익거래_간소.xlsx
@@ -1797,7 +1797,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>[참고] 현물금리 평균</t>
+          <t>▶ 바스켓 평균 현물수익률</t>
         </is>
       </c>
       <c r="B76" s="27">
@@ -1891,7 +1891,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>만기 수익률 shift</t>
+          <t>만기 수익률 shift (현재 현물금리 대비)</t>
         </is>
       </c>
       <c r="B83" s="16" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>만기시점 바스켓 수익률 평행이동</t>
+          <t>0 = 현물금리 무변동.  선도수익률로 수렴하는 경우는 +(선도−현물) bp 를 넣는다</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B84" s="27">
-        <f>B64+B83/100</f>
+        <f>B76+B83/100</f>
         <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -2044,6 +2044,27 @@
       <c r="C92" s="7" t="inlineStr">
         <is>
           <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>참고: 선도수익률 수렴 시 shift</t>
+        </is>
+      </c>
+      <c r="B93" s="29">
+        <f>(B64-B76)*100</f>
+        <v/>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>bp</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>이 값을 B83 에 넣으면 결제가가 이론 선물가격(B66)과 같아진다</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2124,7 @@
         <v>-100</v>
       </c>
       <c r="B96" s="27">
-        <f>$B$64+$A96/100</f>
+        <f>$B$76+$A96/100</f>
         <v/>
       </c>
       <c r="C96" s="27">
@@ -2132,7 +2153,7 @@
         <v>-75</v>
       </c>
       <c r="B97" s="27">
-        <f>$B$64+$A97/100</f>
+        <f>$B$76+$A97/100</f>
         <v/>
       </c>
       <c r="C97" s="27">
@@ -2161,7 +2182,7 @@
         <v>-50</v>
       </c>
       <c r="B98" s="27">
-        <f>$B$64+$A98/100</f>
+        <f>$B$76+$A98/100</f>
         <v/>
       </c>
       <c r="C98" s="27">
@@ -2190,7 +2211,7 @@
         <v>-25</v>
       </c>
       <c r="B99" s="27">
-        <f>$B$64+$A99/100</f>
+        <f>$B$76+$A99/100</f>
         <v/>
       </c>
       <c r="C99" s="27">
@@ -2219,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="B100" s="38">
-        <f>$B$64+$A100/100</f>
+        <f>$B$76+$A100/100</f>
         <v/>
       </c>
       <c r="C100" s="38">
@@ -2248,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="B101" s="27">
-        <f>$B$64+$A101/100</f>
+        <f>$B$76+$A101/100</f>
         <v/>
       </c>
       <c r="C101" s="27">
@@ -2277,7 +2298,7 @@
         <v>50</v>
       </c>
       <c r="B102" s="27">
-        <f>$B$64+$A102/100</f>
+        <f>$B$76+$A102/100</f>
         <v/>
       </c>
       <c r="C102" s="27">
@@ -2306,7 +2327,7 @@
         <v>75</v>
       </c>
       <c r="B103" s="27">
-        <f>$B$64+$A103/100</f>
+        <f>$B$76+$A103/100</f>
         <v/>
       </c>
       <c r="C103" s="27">
@@ -2335,7 +2356,7 @@
         <v>100</v>
       </c>
       <c r="B104" s="27">
-        <f>$B$64+$A104/100</f>
+        <f>$B$76+$A104/100</f>
         <v/>
       </c>
       <c r="C104" s="27">
@@ -3062,43 +3083,43 @@
         <v/>
       </c>
       <c r="S15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+$B$10/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+$B$10/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="T15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$96/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$96/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="U15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$97/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$97/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="V15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$98/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$98/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="W15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$99/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$99/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="X15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$100/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$100/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="Y15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$101/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$101/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="Z15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$102/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$102/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="AA15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$103/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$103/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="AB15" s="43">
-        <f>IF(I15=1,$C15/(1+($B$109+메인!$A$104/10000)/2)^(J15-1),0)</f>
+        <f>IF(I15=1,$C15/(1+($B$8+메인!$A$104/10000)/2)^(J15-1),0)</f>
         <v/>
       </c>
       <c r="AE15" s="41" t="n">
@@ -3173,43 +3194,43 @@
         <v/>
       </c>
       <c r="AW15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+$AF$10/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+$AF$10/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="AX15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$96/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$96/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="AY15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$97/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$97/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="AZ15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$98/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$98/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="BA15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$99/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$99/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="BB15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$100/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$100/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="BC15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$101/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$101/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="BD15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$102/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$102/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="BE15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$103/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$103/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
       <c r="BF15" s="43">
-        <f>IF(AM15=1,$AG15/(1+($AF$109+메인!$A$104/10000)/2)^(AN15-1),0)</f>
+        <f>IF(AM15=1,$AG15/(1+($AF$8+메인!$A$104/10000)/2)^(AN15-1),0)</f>
         <v/>
       </c>
     </row>
@@ -3286,43 +3307,43 @@
         <v/>
       </c>
       <c r="S16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+$B$10/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+$B$10/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="T16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$96/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$96/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="U16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$97/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$97/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="V16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$98/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$98/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="W16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$99/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$99/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="X16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$100/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$100/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="Y16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$101/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$101/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="Z16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$102/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$102/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="AA16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$103/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$103/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="AB16" s="43">
-        <f>IF(I16=1,$C16/(1+($B$109+메인!$A$104/10000)/2)^(J16-1),0)</f>
+        <f>IF(I16=1,$C16/(1+($B$8+메인!$A$104/10000)/2)^(J16-1),0)</f>
         <v/>
       </c>
       <c r="AE16" s="41" t="n">
@@ -3397,43 +3418,43 @@
         <v/>
       </c>
       <c r="AW16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+$AF$10/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+$AF$10/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="AX16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$96/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$96/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="AY16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$97/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$97/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="AZ16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$98/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$98/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="BA16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$99/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$99/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="BB16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$100/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$100/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="BC16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$101/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$101/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="BD16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$102/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$102/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="BE16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$103/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$103/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
       <c r="BF16" s="43">
-        <f>IF(AM16=1,$AG16/(1+($AF$109+메인!$A$104/10000)/2)^(AN16-1),0)</f>
+        <f>IF(AM16=1,$AG16/(1+($AF$8+메인!$A$104/10000)/2)^(AN16-1),0)</f>
         <v/>
       </c>
     </row>
@@ -3510,43 +3531,43 @@
         <v/>
       </c>
       <c r="S17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+$B$10/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+$B$10/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="T17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$96/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$96/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="U17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$97/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$97/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="V17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$98/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$98/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="W17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$99/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$99/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="X17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$100/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$100/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="Y17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$101/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$101/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="Z17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$102/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$102/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="AA17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$103/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$103/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="AB17" s="43">
-        <f>IF(I17=1,$C17/(1+($B$109+메인!$A$104/10000)/2)^(J17-1),0)</f>
+        <f>IF(I17=1,$C17/(1+($B$8+메인!$A$104/10000)/2)^(J17-1),0)</f>
         <v/>
       </c>
       <c r="AE17" s="41" t="n">
@@ -3621,43 +3642,43 @@
         <v/>
       </c>
       <c r="AW17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+$AF$10/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+$AF$10/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="AX17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$96/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$96/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="AY17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$97/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$97/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="AZ17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$98/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$98/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="BA17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$99/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$99/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="BB17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$100/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$100/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="BC17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$101/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$101/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="BD17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$102/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$102/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="BE17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$103/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$103/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
       <c r="BF17" s="43">
-        <f>IF(AM17=1,$AG17/(1+($AF$109+메인!$A$104/10000)/2)^(AN17-1),0)</f>
+        <f>IF(AM17=1,$AG17/(1+($AF$8+메인!$A$104/10000)/2)^(AN17-1),0)</f>
         <v/>
       </c>
     </row>
@@ -3734,43 +3755,43 @@
         <v/>
       </c>
       <c r="S18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+$B$10/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+$B$10/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="T18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$96/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$96/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="U18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$97/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$97/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="V18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$98/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$98/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="W18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$99/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$99/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="X18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$100/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$100/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="Y18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$101/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$101/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="Z18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$102/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$102/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="AA18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$103/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$103/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="AB18" s="43">
-        <f>IF(I18=1,$C18/(1+($B$109+메인!$A$104/10000)/2)^(J18-1),0)</f>
+        <f>IF(I18=1,$C18/(1+($B$8+메인!$A$104/10000)/2)^(J18-1),0)</f>
         <v/>
       </c>
       <c r="AE18" s="41" t="n">
@@ -3845,43 +3866,43 @@
         <v/>
       </c>
       <c r="AW18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+$AF$10/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+$AF$10/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="AX18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$96/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$96/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="AY18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$97/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$97/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="AZ18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$98/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$98/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="BA18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$99/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$99/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="BB18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$100/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$100/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="BC18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$101/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$101/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="BD18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$102/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$102/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="BE18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$103/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$103/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
       <c r="BF18" s="43">
-        <f>IF(AM18=1,$AG18/(1+($AF$109+메인!$A$104/10000)/2)^(AN18-1),0)</f>
+        <f>IF(AM18=1,$AG18/(1+($AF$8+메인!$A$104/10000)/2)^(AN18-1),0)</f>
         <v/>
       </c>
     </row>
@@ -3958,43 +3979,43 @@
         <v/>
       </c>
       <c r="S19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+$B$10/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+$B$10/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="T19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$96/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$96/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="U19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$97/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$97/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="V19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$98/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$98/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="W19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$99/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$99/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="X19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$100/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$100/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="Y19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$101/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$101/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="Z19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$102/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$102/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="AA19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$103/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$103/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="AB19" s="43">
-        <f>IF(I19=1,$C19/(1+($B$109+메인!$A$104/10000)/2)^(J19-1),0)</f>
+        <f>IF(I19=1,$C19/(1+($B$8+메인!$A$104/10000)/2)^(J19-1),0)</f>
         <v/>
       </c>
       <c r="AE19" s="41" t="n">
@@ -4069,43 +4090,43 @@
         <v/>
       </c>
       <c r="AW19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+$AF$10/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+$AF$10/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="AX19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$96/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$96/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="AY19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$97/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$97/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="AZ19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$98/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$98/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="BA19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$99/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$99/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="BB19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$100/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$100/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="BC19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$101/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$101/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="BD19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$102/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$102/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="BE19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$103/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$103/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
       <c r="BF19" s="43">
-        <f>IF(AM19=1,$AG19/(1+($AF$109+메인!$A$104/10000)/2)^(AN19-1),0)</f>
+        <f>IF(AM19=1,$AG19/(1+($AF$8+메인!$A$104/10000)/2)^(AN19-1),0)</f>
         <v/>
       </c>
     </row>
@@ -4182,43 +4203,43 @@
         <v/>
       </c>
       <c r="S20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+$B$10/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+$B$10/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="T20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$96/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$96/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="U20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$97/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$97/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="V20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$98/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$98/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="W20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$99/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$99/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="X20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$100/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$100/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="Y20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$101/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$101/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="Z20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$102/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$102/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="AA20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$103/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$103/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="AB20" s="43">
-        <f>IF(I20=1,$C20/(1+($B$109+메인!$A$104/10000)/2)^(J20-1),0)</f>
+        <f>IF(I20=1,$C20/(1+($B$8+메인!$A$104/10000)/2)^(J20-1),0)</f>
         <v/>
       </c>
       <c r="AE20" s="41" t="n">
@@ -4293,43 +4314,43 @@
         <v/>
       </c>
       <c r="AW20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+$AF$10/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+$AF$10/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="AX20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$96/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$96/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="AY20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$97/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$97/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="AZ20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$98/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$98/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="BA20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$99/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$99/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="BB20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$100/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$100/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="BC20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$101/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$101/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="BD20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$102/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$102/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="BE20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$103/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$103/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
       <c r="BF20" s="43">
-        <f>IF(AM20=1,$AG20/(1+($AF$109+메인!$A$104/10000)/2)^(AN20-1),0)</f>
+        <f>IF(AM20=1,$AG20/(1+($AF$8+메인!$A$104/10000)/2)^(AN20-1),0)</f>
         <v/>
       </c>
     </row>
@@ -4406,43 +4427,43 @@
         <v/>
       </c>
       <c r="S21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+$B$10/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+$B$10/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="T21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$96/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$96/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="U21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$97/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$97/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="V21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$98/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$98/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="W21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$99/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$99/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="X21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$100/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$100/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="Y21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$101/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$101/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="Z21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$102/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$102/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="AA21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$103/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$103/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="AB21" s="43">
-        <f>IF(I21=1,$C21/(1+($B$109+메인!$A$104/10000)/2)^(J21-1),0)</f>
+        <f>IF(I21=1,$C21/(1+($B$8+메인!$A$104/10000)/2)^(J21-1),0)</f>
         <v/>
       </c>
       <c r="AE21" s="41" t="n">
@@ -4517,43 +4538,43 @@
         <v/>
       </c>
       <c r="AW21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+$AF$10/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+$AF$10/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="AX21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$96/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$96/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="AY21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$97/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$97/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="AZ21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$98/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$98/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="BA21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$99/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$99/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="BB21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$100/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$100/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="BC21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$101/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$101/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="BD21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$102/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$102/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="BE21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$103/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$103/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
       <c r="BF21" s="43">
-        <f>IF(AM21=1,$AG21/(1+($AF$109+메인!$A$104/10000)/2)^(AN21-1),0)</f>
+        <f>IF(AM21=1,$AG21/(1+($AF$8+메인!$A$104/10000)/2)^(AN21-1),0)</f>
         <v/>
       </c>
     </row>
@@ -4630,43 +4651,43 @@
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+$B$10/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+$B$10/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="T22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$96/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$96/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$97/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$97/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="V22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$98/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$98/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$99/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$99/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$100/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$100/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$101/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$101/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="Z22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$102/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$102/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$103/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$103/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="AB22" s="43">
-        <f>IF(I22=1,$C22/(1+($B$109+메인!$A$104/10000)/2)^(J22-1),0)</f>
+        <f>IF(I22=1,$C22/(1+($B$8+메인!$A$104/10000)/2)^(J22-1),0)</f>
         <v/>
       </c>
       <c r="AE22" s="41" t="n">
@@ -4741,43 +4762,43 @@
         <v/>
       </c>
       <c r="AW22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+$AF$10/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+$AF$10/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="AX22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$96/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$96/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="AY22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$97/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$97/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="AZ22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$98/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$98/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="BA22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$99/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$99/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="BB22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$100/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$100/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="BC22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$101/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$101/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="BD22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$102/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$102/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="BE22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$103/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$103/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
       <c r="BF22" s="43">
-        <f>IF(AM22=1,$AG22/(1+($AF$109+메인!$A$104/10000)/2)^(AN22-1),0)</f>
+        <f>IF(AM22=1,$AG22/(1+($AF$8+메인!$A$104/10000)/2)^(AN22-1),0)</f>
         <v/>
       </c>
     </row>
@@ -4854,43 +4875,43 @@
         <v/>
       </c>
       <c r="S23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+$B$10/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+$B$10/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="T23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$96/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$96/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="U23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$97/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$97/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="V23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$98/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$98/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="W23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$99/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$99/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$100/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$100/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="Y23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$101/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$101/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="Z23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$102/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$102/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="AA23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$103/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$103/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="AB23" s="43">
-        <f>IF(I23=1,$C23/(1+($B$109+메인!$A$104/10000)/2)^(J23-1),0)</f>
+        <f>IF(I23=1,$C23/(1+($B$8+메인!$A$104/10000)/2)^(J23-1),0)</f>
         <v/>
       </c>
       <c r="AE23" s="41" t="n">
@@ -4965,43 +4986,43 @@
         <v/>
       </c>
       <c r="AW23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+$AF$10/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+$AF$10/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="AX23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$96/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$96/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="AY23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$97/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$97/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="AZ23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$98/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$98/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="BA23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$99/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$99/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="BB23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$100/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$100/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="BC23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$101/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$101/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="BD23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$102/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$102/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="BE23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$103/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$103/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
       <c r="BF23" s="43">
-        <f>IF(AM23=1,$AG23/(1+($AF$109+메인!$A$104/10000)/2)^(AN23-1),0)</f>
+        <f>IF(AM23=1,$AG23/(1+($AF$8+메인!$A$104/10000)/2)^(AN23-1),0)</f>
         <v/>
       </c>
     </row>
@@ -5078,43 +5099,43 @@
         <v/>
       </c>
       <c r="S24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+$B$10/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+$B$10/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="T24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$96/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$96/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="U24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$97/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$97/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="V24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$98/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$98/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="W24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$99/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$99/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="X24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$100/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$100/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="Y24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$101/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$101/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="Z24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$102/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$102/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="AA24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$103/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$103/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="AB24" s="43">
-        <f>IF(I24=1,$C24/(1+($B$109+메인!$A$104/10000)/2)^(J24-1),0)</f>
+        <f>IF(I24=1,$C24/(1+($B$8+메인!$A$104/10000)/2)^(J24-1),0)</f>
         <v/>
       </c>
       <c r="AE24" s="41" t="n">
@@ -5189,43 +5210,43 @@
         <v/>
       </c>
       <c r="AW24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+$AF$10/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+$AF$10/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="AX24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$96/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$96/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="AY24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$97/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$97/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="AZ24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$98/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$98/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="BA24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$99/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$99/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="BB24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$100/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$100/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="BC24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$101/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$101/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="BD24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$102/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$102/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="BE24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$103/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$103/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
       <c r="BF24" s="43">
-        <f>IF(AM24=1,$AG24/(1+($AF$109+메인!$A$104/10000)/2)^(AN24-1),0)</f>
+        <f>IF(AM24=1,$AG24/(1+($AF$8+메인!$A$104/10000)/2)^(AN24-1),0)</f>
         <v/>
       </c>
     </row>
@@ -5302,43 +5323,43 @@
         <v/>
       </c>
       <c r="S25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+$B$10/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+$B$10/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="T25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$96/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$96/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="U25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$97/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$97/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="V25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$98/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$98/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="W25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$99/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$99/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="X25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$100/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$100/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="Y25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$101/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$101/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="Z25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$102/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$102/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="AA25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$103/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$103/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="AB25" s="43">
-        <f>IF(I25=1,$C25/(1+($B$109+메인!$A$104/10000)/2)^(J25-1),0)</f>
+        <f>IF(I25=1,$C25/(1+($B$8+메인!$A$104/10000)/2)^(J25-1),0)</f>
         <v/>
       </c>
       <c r="AE25" s="41" t="n">
@@ -5413,43 +5434,43 @@
         <v/>
       </c>
       <c r="AW25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+$AF$10/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+$AF$10/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="AX25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$96/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$96/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="AY25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$97/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$97/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="AZ25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$98/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$98/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="BA25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$99/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$99/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="BB25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$100/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$100/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="BC25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$101/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$101/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="BD25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$102/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$102/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="BE25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$103/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$103/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
       <c r="BF25" s="43">
-        <f>IF(AM25=1,$AG25/(1+($AF$109+메인!$A$104/10000)/2)^(AN25-1),0)</f>
+        <f>IF(AM25=1,$AG25/(1+($AF$8+메인!$A$104/10000)/2)^(AN25-1),0)</f>
         <v/>
       </c>
     </row>
@@ -5526,43 +5547,43 @@
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+$B$10/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+$B$10/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$96/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$96/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$97/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$97/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$98/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$98/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$99/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$99/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$100/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$100/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$101/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$101/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$102/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$102/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$103/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$103/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>IF(I26=1,$C26/(1+($B$109+메인!$A$104/10000)/2)^(J26-1),0)</f>
+        <f>IF(I26=1,$C26/(1+($B$8+메인!$A$104/10000)/2)^(J26-1),0)</f>
         <v/>
       </c>
       <c r="AE26" s="41" t="n">
@@ -5637,43 +5658,43 @@
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+$AF$10/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+$AF$10/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$96/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$96/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$97/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$97/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$98/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$98/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$99/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$99/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$100/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$100/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$101/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$101/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$102/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$102/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$103/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$103/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>IF(AM26=1,$AG26/(1+($AF$109+메인!$A$104/10000)/2)^(AN26-1),0)</f>
+        <f>IF(AM26=1,$AG26/(1+($AF$8+메인!$A$104/10000)/2)^(AN26-1),0)</f>
         <v/>
       </c>
     </row>
@@ -5750,43 +5771,43 @@
         <v/>
       </c>
       <c r="S27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+$B$10/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+$B$10/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="T27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$96/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$96/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="U27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$97/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$97/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="V27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$98/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$98/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="W27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$99/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$99/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="X27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$100/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$100/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="Y27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$101/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$101/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="Z27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$102/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$102/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="AA27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$103/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$103/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="AB27" s="43">
-        <f>IF(I27=1,$C27/(1+($B$109+메인!$A$104/10000)/2)^(J27-1),0)</f>
+        <f>IF(I27=1,$C27/(1+($B$8+메인!$A$104/10000)/2)^(J27-1),0)</f>
         <v/>
       </c>
       <c r="AE27" s="41" t="n">
@@ -5861,43 +5882,43 @@
         <v/>
       </c>
       <c r="AW27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+$AF$10/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+$AF$10/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="AX27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$96/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$96/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="AY27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$97/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$97/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="AZ27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$98/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$98/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="BA27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$99/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$99/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="BB27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$100/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$100/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="BC27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$101/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$101/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="BD27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$102/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$102/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="BE27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$103/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$103/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
       <c r="BF27" s="43">
-        <f>IF(AM27=1,$AG27/(1+($AF$109+메인!$A$104/10000)/2)^(AN27-1),0)</f>
+        <f>IF(AM27=1,$AG27/(1+($AF$8+메인!$A$104/10000)/2)^(AN27-1),0)</f>
         <v/>
       </c>
     </row>
@@ -5974,43 +5995,43 @@
         <v/>
       </c>
       <c r="S28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+$B$10/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+$B$10/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="T28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$96/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$96/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="U28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$97/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$97/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="V28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$98/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$98/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="W28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$99/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$99/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="X28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$100/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$100/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="Y28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$101/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$101/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="Z28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$102/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$102/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="AA28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$103/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$103/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="AB28" s="43">
-        <f>IF(I28=1,$C28/(1+($B$109+메인!$A$104/10000)/2)^(J28-1),0)</f>
+        <f>IF(I28=1,$C28/(1+($B$8+메인!$A$104/10000)/2)^(J28-1),0)</f>
         <v/>
       </c>
       <c r="AE28" s="41" t="n">
@@ -6085,43 +6106,43 @@
         <v/>
       </c>
       <c r="AW28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+$AF$10/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+$AF$10/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="AX28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$96/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$96/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="AY28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$97/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$97/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="AZ28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$98/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$98/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="BA28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$99/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$99/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="BB28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$100/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$100/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="BC28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$101/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$101/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="BD28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$102/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$102/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="BE28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$103/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$103/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
       <c r="BF28" s="43">
-        <f>IF(AM28=1,$AG28/(1+($AF$109+메인!$A$104/10000)/2)^(AN28-1),0)</f>
+        <f>IF(AM28=1,$AG28/(1+($AF$8+메인!$A$104/10000)/2)^(AN28-1),0)</f>
         <v/>
       </c>
     </row>
@@ -6198,43 +6219,43 @@
         <v/>
       </c>
       <c r="S29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+$B$10/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+$B$10/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="T29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$96/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$96/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="U29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$97/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$97/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="V29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$98/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$98/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="W29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$99/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$99/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="X29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$100/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$100/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="Y29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$101/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$101/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="Z29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$102/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$102/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="AA29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$103/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$103/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="AB29" s="43">
-        <f>IF(I29=1,$C29/(1+($B$109+메인!$A$104/10000)/2)^(J29-1),0)</f>
+        <f>IF(I29=1,$C29/(1+($B$8+메인!$A$104/10000)/2)^(J29-1),0)</f>
         <v/>
       </c>
       <c r="AE29" s="41" t="n">
@@ -6309,43 +6330,43 @@
         <v/>
       </c>
       <c r="AW29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+$AF$10/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+$AF$10/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="AX29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$96/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$96/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="AY29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$97/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$97/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="AZ29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$98/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$98/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="BA29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$99/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$99/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="BB29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$100/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$100/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="BC29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$101/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$101/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="BD29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$102/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$102/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="BE29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$103/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$103/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
       <c r="BF29" s="43">
-        <f>IF(AM29=1,$AG29/(1+($AF$109+메인!$A$104/10000)/2)^(AN29-1),0)</f>
+        <f>IF(AM29=1,$AG29/(1+($AF$8+메인!$A$104/10000)/2)^(AN29-1),0)</f>
         <v/>
       </c>
     </row>
@@ -6422,43 +6443,43 @@
         <v/>
       </c>
       <c r="S30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+$B$10/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+$B$10/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="T30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$96/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$96/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="U30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$97/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$97/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="V30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$98/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$98/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="W30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$99/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$99/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="X30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$100/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$100/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="Y30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$101/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$101/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="Z30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$102/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$102/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="AA30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$103/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$103/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="AB30" s="43">
-        <f>IF(I30=1,$C30/(1+($B$109+메인!$A$104/10000)/2)^(J30-1),0)</f>
+        <f>IF(I30=1,$C30/(1+($B$8+메인!$A$104/10000)/2)^(J30-1),0)</f>
         <v/>
       </c>
       <c r="AE30" s="41" t="n">
@@ -6533,43 +6554,43 @@
         <v/>
       </c>
       <c r="AW30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+$AF$10/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+$AF$10/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="AX30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$96/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$96/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="AY30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$97/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$97/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="AZ30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$98/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$98/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="BA30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$99/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$99/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="BB30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$100/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$100/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="BC30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$101/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$101/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="BD30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$102/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$102/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="BE30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$103/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$103/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
       <c r="BF30" s="43">
-        <f>IF(AM30=1,$AG30/(1+($AF$109+메인!$A$104/10000)/2)^(AN30-1),0)</f>
+        <f>IF(AM30=1,$AG30/(1+($AF$8+메인!$A$104/10000)/2)^(AN30-1),0)</f>
         <v/>
       </c>
     </row>
@@ -6646,43 +6667,43 @@
         <v/>
       </c>
       <c r="S31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+$B$10/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+$B$10/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="T31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$96/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$96/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="U31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$97/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$97/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="V31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$98/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$98/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="W31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$99/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$99/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="X31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$100/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$100/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="Y31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$101/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$101/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="Z31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$102/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$102/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="AA31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$103/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$103/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="AB31" s="43">
-        <f>IF(I31=1,$C31/(1+($B$109+메인!$A$104/10000)/2)^(J31-1),0)</f>
+        <f>IF(I31=1,$C31/(1+($B$8+메인!$A$104/10000)/2)^(J31-1),0)</f>
         <v/>
       </c>
       <c r="AE31" s="41" t="n">
@@ -6757,43 +6778,43 @@
         <v/>
       </c>
       <c r="AW31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+$AF$10/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+$AF$10/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="AX31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$96/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$96/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="AY31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$97/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$97/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="AZ31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$98/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$98/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="BA31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$99/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$99/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="BB31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$100/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$100/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="BC31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$101/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$101/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="BD31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$102/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$102/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="BE31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$103/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$103/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
       <c r="BF31" s="43">
-        <f>IF(AM31=1,$AG31/(1+($AF$109+메인!$A$104/10000)/2)^(AN31-1),0)</f>
+        <f>IF(AM31=1,$AG31/(1+($AF$8+메인!$A$104/10000)/2)^(AN31-1),0)</f>
         <v/>
       </c>
     </row>
@@ -6870,43 +6891,43 @@
         <v/>
       </c>
       <c r="S32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+$B$10/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+$B$10/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="T32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$96/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$96/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="U32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$97/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$97/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="V32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$98/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$98/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="W32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$99/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$99/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="X32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$100/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$100/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="Y32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$101/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$101/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="Z32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$102/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$102/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="AA32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$103/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$103/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="AB32" s="43">
-        <f>IF(I32=1,$C32/(1+($B$109+메인!$A$104/10000)/2)^(J32-1),0)</f>
+        <f>IF(I32=1,$C32/(1+($B$8+메인!$A$104/10000)/2)^(J32-1),0)</f>
         <v/>
       </c>
       <c r="AE32" s="41" t="n">
@@ -6981,43 +7002,43 @@
         <v/>
       </c>
       <c r="AW32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+$AF$10/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+$AF$10/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="AX32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$96/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$96/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="AY32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$97/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$97/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="AZ32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$98/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$98/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="BA32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$99/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$99/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="BB32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$100/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$100/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="BC32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$101/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$101/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="BD32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$102/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$102/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="BE32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$103/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$103/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
       <c r="BF32" s="43">
-        <f>IF(AM32=1,$AG32/(1+($AF$109+메인!$A$104/10000)/2)^(AN32-1),0)</f>
+        <f>IF(AM32=1,$AG32/(1+($AF$8+메인!$A$104/10000)/2)^(AN32-1),0)</f>
         <v/>
       </c>
     </row>
@@ -7094,43 +7115,43 @@
         <v/>
       </c>
       <c r="S33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+$B$10/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+$B$10/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="T33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$96/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$96/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="U33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$97/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$97/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="V33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$98/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$98/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="W33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$99/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$99/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="X33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$100/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$100/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="Y33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$101/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$101/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="Z33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$102/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$102/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="AA33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$103/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$103/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="AB33" s="43">
-        <f>IF(I33=1,$C33/(1+($B$109+메인!$A$104/10000)/2)^(J33-1),0)</f>
+        <f>IF(I33=1,$C33/(1+($B$8+메인!$A$104/10000)/2)^(J33-1),0)</f>
         <v/>
       </c>
       <c r="AE33" s="41" t="n">
@@ -7205,43 +7226,43 @@
         <v/>
       </c>
       <c r="AW33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+$AF$10/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+$AF$10/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="AX33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$96/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$96/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="AY33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$97/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$97/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="AZ33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$98/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$98/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="BA33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$99/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$99/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="BB33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$100/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$100/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="BC33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$101/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$101/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="BD33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$102/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$102/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="BE33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$103/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$103/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
       <c r="BF33" s="43">
-        <f>IF(AM33=1,$AG33/(1+($AF$109+메인!$A$104/10000)/2)^(AN33-1),0)</f>
+        <f>IF(AM33=1,$AG33/(1+($AF$8+메인!$A$104/10000)/2)^(AN33-1),0)</f>
         <v/>
       </c>
     </row>
@@ -7318,43 +7339,43 @@
         <v/>
       </c>
       <c r="S34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+$B$10/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+$B$10/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="T34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$96/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$96/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="U34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$97/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$97/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="V34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$98/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$98/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="W34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$99/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$99/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="X34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$100/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$100/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="Y34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$101/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$101/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="Z34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$102/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$102/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="AA34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$103/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$103/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="AB34" s="43">
-        <f>IF(I34=1,$C34/(1+($B$109+메인!$A$104/10000)/2)^(J34-1),0)</f>
+        <f>IF(I34=1,$C34/(1+($B$8+메인!$A$104/10000)/2)^(J34-1),0)</f>
         <v/>
       </c>
       <c r="AE34" s="41" t="n">
@@ -7429,43 +7450,43 @@
         <v/>
       </c>
       <c r="AW34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+$AF$10/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+$AF$10/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="AX34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$96/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$96/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="AY34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$97/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$97/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="AZ34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$98/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$98/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="BA34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$99/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$99/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="BB34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$100/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$100/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="BC34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$101/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$101/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="BD34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$102/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$102/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="BE34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$103/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$103/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
       <c r="BF34" s="43">
-        <f>IF(AM34=1,$AG34/(1+($AF$109+메인!$A$104/10000)/2)^(AN34-1),0)</f>
+        <f>IF(AM34=1,$AG34/(1+($AF$8+메인!$A$104/10000)/2)^(AN34-1),0)</f>
         <v/>
       </c>
     </row>
@@ -7542,43 +7563,43 @@
         <v/>
       </c>
       <c r="S35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+$B$10/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+$B$10/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="T35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$96/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$96/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="U35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$97/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$97/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="V35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$98/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$98/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="W35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$99/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$99/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="X35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$100/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$100/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="Y35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$101/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$101/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="Z35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$102/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$102/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="AA35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$103/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$103/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="AB35" s="43">
-        <f>IF(I35=1,$C35/(1+($B$109+메인!$A$104/10000)/2)^(J35-1),0)</f>
+        <f>IF(I35=1,$C35/(1+($B$8+메인!$A$104/10000)/2)^(J35-1),0)</f>
         <v/>
       </c>
       <c r="AE35" s="41" t="n">
@@ -7653,43 +7674,43 @@
         <v/>
       </c>
       <c r="AW35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+$AF$10/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+$AF$10/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="AX35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$96/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$96/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="AY35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$97/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$97/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="AZ35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$98/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$98/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="BA35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$99/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$99/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="BB35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$100/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$100/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="BC35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$101/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$101/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="BD35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$102/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$102/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="BE35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$103/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$103/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
       <c r="BF35" s="43">
-        <f>IF(AM35=1,$AG35/(1+($AF$109+메인!$A$104/10000)/2)^(AN35-1),0)</f>
+        <f>IF(AM35=1,$AG35/(1+($AF$8+메인!$A$104/10000)/2)^(AN35-1),0)</f>
         <v/>
       </c>
     </row>
@@ -7766,43 +7787,43 @@
         <v/>
       </c>
       <c r="S36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+$B$10/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+$B$10/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="T36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$96/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$96/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="U36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$97/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$97/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="V36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$98/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$98/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="W36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$99/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$99/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="X36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$100/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$100/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="Y36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$101/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$101/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="Z36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$102/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$102/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="AA36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$103/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$103/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="AB36" s="43">
-        <f>IF(I36=1,$C36/(1+($B$109+메인!$A$104/10000)/2)^(J36-1),0)</f>
+        <f>IF(I36=1,$C36/(1+($B$8+메인!$A$104/10000)/2)^(J36-1),0)</f>
         <v/>
       </c>
       <c r="AE36" s="41" t="n">
@@ -7877,43 +7898,43 @@
         <v/>
       </c>
       <c r="AW36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+$AF$10/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+$AF$10/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="AX36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$96/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$96/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="AY36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$97/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$97/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="AZ36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$98/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$98/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="BA36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$99/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$99/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="BB36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$100/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$100/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="BC36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$101/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$101/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="BD36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$102/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$102/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="BE36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$103/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$103/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
       <c r="BF36" s="43">
-        <f>IF(AM36=1,$AG36/(1+($AF$109+메인!$A$104/10000)/2)^(AN36-1),0)</f>
+        <f>IF(AM36=1,$AG36/(1+($AF$8+메인!$A$104/10000)/2)^(AN36-1),0)</f>
         <v/>
       </c>
     </row>
@@ -7990,43 +8011,43 @@
         <v/>
       </c>
       <c r="S37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+$B$10/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+$B$10/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="T37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$96/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$96/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="U37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$97/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$97/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="V37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$98/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$98/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="W37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$99/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$99/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="X37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$100/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$100/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="Y37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$101/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$101/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="Z37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$102/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$102/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="AA37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$103/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$103/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="AB37" s="43">
-        <f>IF(I37=1,$C37/(1+($B$109+메인!$A$104/10000)/2)^(J37-1),0)</f>
+        <f>IF(I37=1,$C37/(1+($B$8+메인!$A$104/10000)/2)^(J37-1),0)</f>
         <v/>
       </c>
       <c r="AE37" s="41" t="n">
@@ -8101,43 +8122,43 @@
         <v/>
       </c>
       <c r="AW37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+$AF$10/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+$AF$10/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="AX37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$96/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$96/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="AY37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$97/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$97/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="AZ37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$98/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$98/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="BA37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$99/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$99/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="BB37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$100/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$100/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="BC37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$101/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$101/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="BD37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$102/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$102/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="BE37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$103/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$103/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
       <c r="BF37" s="43">
-        <f>IF(AM37=1,$AG37/(1+($AF$109+메인!$A$104/10000)/2)^(AN37-1),0)</f>
+        <f>IF(AM37=1,$AG37/(1+($AF$8+메인!$A$104/10000)/2)^(AN37-1),0)</f>
         <v/>
       </c>
     </row>
@@ -8214,43 +8235,43 @@
         <v/>
       </c>
       <c r="S38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+$B$10/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+$B$10/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="T38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$96/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$96/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="U38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$97/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$97/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="V38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$98/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$98/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="W38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$99/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$99/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="X38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$100/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$100/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="Y38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$101/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$101/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="Z38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$102/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$102/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="AA38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$103/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$103/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="AB38" s="43">
-        <f>IF(I38=1,$C38/(1+($B$109+메인!$A$104/10000)/2)^(J38-1),0)</f>
+        <f>IF(I38=1,$C38/(1+($B$8+메인!$A$104/10000)/2)^(J38-1),0)</f>
         <v/>
       </c>
       <c r="AE38" s="41" t="n">
@@ -8325,43 +8346,43 @@
         <v/>
       </c>
       <c r="AW38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+$AF$10/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+$AF$10/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="AX38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$96/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$96/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="AY38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$97/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$97/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="AZ38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$98/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$98/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="BA38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$99/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$99/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="BB38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$100/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$100/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="BC38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$101/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$101/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="BD38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$102/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$102/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="BE38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$103/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$103/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
       <c r="BF38" s="43">
-        <f>IF(AM38=1,$AG38/(1+($AF$109+메인!$A$104/10000)/2)^(AN38-1),0)</f>
+        <f>IF(AM38=1,$AG38/(1+($AF$8+메인!$A$104/10000)/2)^(AN38-1),0)</f>
         <v/>
       </c>
     </row>
@@ -8438,43 +8459,43 @@
         <v/>
       </c>
       <c r="S39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+$B$10/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+$B$10/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="T39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$96/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$96/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="U39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$97/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$97/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="V39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$98/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$98/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="W39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$99/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$99/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="X39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$100/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$100/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="Y39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$101/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$101/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="Z39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$102/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$102/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="AA39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$103/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$103/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="AB39" s="43">
-        <f>IF(I39=1,$C39/(1+($B$109+메인!$A$104/10000)/2)^(J39-1),0)</f>
+        <f>IF(I39=1,$C39/(1+($B$8+메인!$A$104/10000)/2)^(J39-1),0)</f>
         <v/>
       </c>
       <c r="AE39" s="41" t="n">
@@ -8549,43 +8570,43 @@
         <v/>
       </c>
       <c r="AW39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+$AF$10/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+$AF$10/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="AX39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$96/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$96/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="AY39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$97/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$97/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="AZ39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$98/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$98/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="BA39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$99/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$99/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="BB39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$100/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$100/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="BC39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$101/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$101/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="BD39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$102/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$102/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="BE39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$103/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$103/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
       <c r="BF39" s="43">
-        <f>IF(AM39=1,$AG39/(1+($AF$109+메인!$A$104/10000)/2)^(AN39-1),0)</f>
+        <f>IF(AM39=1,$AG39/(1+($AF$8+메인!$A$104/10000)/2)^(AN39-1),0)</f>
         <v/>
       </c>
     </row>
@@ -8662,43 +8683,43 @@
         <v/>
       </c>
       <c r="S40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+$B$10/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+$B$10/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="T40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$96/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$96/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="U40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$97/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$97/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="V40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$98/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$98/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="W40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$99/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$99/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="X40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$100/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$100/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="Y40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$101/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$101/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="Z40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$102/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$102/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="AA40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$103/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$103/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="AB40" s="43">
-        <f>IF(I40=1,$C40/(1+($B$109+메인!$A$104/10000)/2)^(J40-1),0)</f>
+        <f>IF(I40=1,$C40/(1+($B$8+메인!$A$104/10000)/2)^(J40-1),0)</f>
         <v/>
       </c>
       <c r="AE40" s="41" t="n">
@@ -8773,43 +8794,43 @@
         <v/>
       </c>
       <c r="AW40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+$AF$10/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+$AF$10/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="AX40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$96/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$96/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="AY40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$97/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$97/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="AZ40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$98/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$98/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="BA40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$99/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$99/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="BB40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$100/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$100/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="BC40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$101/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$101/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="BD40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$102/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$102/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="BE40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$103/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$103/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
       <c r="BF40" s="43">
-        <f>IF(AM40=1,$AG40/(1+($AF$109+메인!$A$104/10000)/2)^(AN40-1),0)</f>
+        <f>IF(AM40=1,$AG40/(1+($AF$8+메인!$A$104/10000)/2)^(AN40-1),0)</f>
         <v/>
       </c>
     </row>
@@ -8886,43 +8907,43 @@
         <v/>
       </c>
       <c r="S41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+$B$10/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+$B$10/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="T41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$96/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$96/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="U41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$97/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$97/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="V41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$98/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$98/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="W41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$99/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$99/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="X41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$100/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$100/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="Y41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$101/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$101/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="Z41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$102/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$102/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="AA41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$103/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$103/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="AB41" s="43">
-        <f>IF(I41=1,$C41/(1+($B$109+메인!$A$104/10000)/2)^(J41-1),0)</f>
+        <f>IF(I41=1,$C41/(1+($B$8+메인!$A$104/10000)/2)^(J41-1),0)</f>
         <v/>
       </c>
       <c r="AE41" s="41" t="n">
@@ -8997,43 +9018,43 @@
         <v/>
       </c>
       <c r="AW41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+$AF$10/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+$AF$10/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="AX41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$96/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$96/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="AY41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$97/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$97/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="AZ41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$98/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$98/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="BA41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$99/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$99/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="BB41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$100/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$100/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="BC41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$101/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$101/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="BD41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$102/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$102/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="BE41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$103/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$103/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
       <c r="BF41" s="43">
-        <f>IF(AM41=1,$AG41/(1+($AF$109+메인!$A$104/10000)/2)^(AN41-1),0)</f>
+        <f>IF(AM41=1,$AG41/(1+($AF$8+메인!$A$104/10000)/2)^(AN41-1),0)</f>
         <v/>
       </c>
     </row>
@@ -9110,43 +9131,43 @@
         <v/>
       </c>
       <c r="S42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+$B$10/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+$B$10/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="T42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$96/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$96/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="U42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$97/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$97/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="V42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$98/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$98/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="W42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$99/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$99/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="X42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$100/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$100/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="Y42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$101/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$101/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="Z42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$102/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$102/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="AA42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$103/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$103/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="AB42" s="43">
-        <f>IF(I42=1,$C42/(1+($B$109+메인!$A$104/10000)/2)^(J42-1),0)</f>
+        <f>IF(I42=1,$C42/(1+($B$8+메인!$A$104/10000)/2)^(J42-1),0)</f>
         <v/>
       </c>
       <c r="AE42" s="41" t="n">
@@ -9221,43 +9242,43 @@
         <v/>
       </c>
       <c r="AW42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+$AF$10/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+$AF$10/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="AX42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$96/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$96/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="AY42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$97/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$97/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="AZ42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$98/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$98/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="BA42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$99/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$99/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="BB42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$100/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$100/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="BC42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$101/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$101/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="BD42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$102/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$102/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="BE42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$103/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$103/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
       <c r="BF42" s="43">
-        <f>IF(AM42=1,$AG42/(1+($AF$109+메인!$A$104/10000)/2)^(AN42-1),0)</f>
+        <f>IF(AM42=1,$AG42/(1+($AF$8+메인!$A$104/10000)/2)^(AN42-1),0)</f>
         <v/>
       </c>
     </row>
@@ -9334,43 +9355,43 @@
         <v/>
       </c>
       <c r="S43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+$B$10/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+$B$10/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="T43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$96/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$96/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="U43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$97/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$97/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="V43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$98/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$98/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="W43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$99/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$99/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="X43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$100/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$100/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="Y43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$101/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$101/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="Z43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$102/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$102/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="AA43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$103/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$103/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="AB43" s="43">
-        <f>IF(I43=1,$C43/(1+($B$109+메인!$A$104/10000)/2)^(J43-1),0)</f>
+        <f>IF(I43=1,$C43/(1+($B$8+메인!$A$104/10000)/2)^(J43-1),0)</f>
         <v/>
       </c>
       <c r="AE43" s="41" t="n">
@@ -9445,43 +9466,43 @@
         <v/>
       </c>
       <c r="AW43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+$AF$10/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+$AF$10/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="AX43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$96/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$96/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="AY43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$97/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$97/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="AZ43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$98/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$98/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="BA43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$99/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$99/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="BB43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$100/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$100/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="BC43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$101/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$101/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="BD43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$102/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$102/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="BE43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$103/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$103/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
       <c r="BF43" s="43">
-        <f>IF(AM43=1,$AG43/(1+($AF$109+메인!$A$104/10000)/2)^(AN43-1),0)</f>
+        <f>IF(AM43=1,$AG43/(1+($AF$8+메인!$A$104/10000)/2)^(AN43-1),0)</f>
         <v/>
       </c>
     </row>
@@ -9558,43 +9579,43 @@
         <v/>
       </c>
       <c r="S44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+$B$10/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+$B$10/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="T44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$96/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$96/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="U44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$97/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$97/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="V44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$98/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$98/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="W44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$99/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$99/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="X44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$100/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$100/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="Y44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$101/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$101/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="Z44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$102/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$102/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="AA44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$103/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$103/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="AB44" s="43">
-        <f>IF(I44=1,$C44/(1+($B$109+메인!$A$104/10000)/2)^(J44-1),0)</f>
+        <f>IF(I44=1,$C44/(1+($B$8+메인!$A$104/10000)/2)^(J44-1),0)</f>
         <v/>
       </c>
       <c r="AE44" s="41" t="n">
@@ -9669,43 +9690,43 @@
         <v/>
       </c>
       <c r="AW44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+$AF$10/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+$AF$10/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="AX44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$96/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$96/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="AY44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$97/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$97/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="AZ44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$98/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$98/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="BA44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$99/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$99/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="BB44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$100/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$100/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="BC44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$101/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$101/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="BD44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$102/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$102/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="BE44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$103/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$103/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
       <c r="BF44" s="43">
-        <f>IF(AM44=1,$AG44/(1+($AF$109+메인!$A$104/10000)/2)^(AN44-1),0)</f>
+        <f>IF(AM44=1,$AG44/(1+($AF$8+메인!$A$104/10000)/2)^(AN44-1),0)</f>
         <v/>
       </c>
     </row>
@@ -9782,43 +9803,43 @@
         <v/>
       </c>
       <c r="S45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+$B$10/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+$B$10/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="T45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$96/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$96/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="U45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$97/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$97/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="V45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$98/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$98/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="W45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$99/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$99/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="X45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$100/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$100/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="Y45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$101/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$101/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="Z45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$102/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$102/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="AA45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$103/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$103/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="AB45" s="43">
-        <f>IF(I45=1,$C45/(1+($B$109+메인!$A$104/10000)/2)^(J45-1),0)</f>
+        <f>IF(I45=1,$C45/(1+($B$8+메인!$A$104/10000)/2)^(J45-1),0)</f>
         <v/>
       </c>
       <c r="AE45" s="41" t="n">
@@ -9893,43 +9914,43 @@
         <v/>
       </c>
       <c r="AW45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+$AF$10/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+$AF$10/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="AX45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$96/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$96/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="AY45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$97/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$97/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="AZ45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$98/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$98/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="BA45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$99/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$99/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="BB45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$100/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$100/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="BC45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$101/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$101/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="BD45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$102/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$102/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="BE45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$103/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$103/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
       <c r="BF45" s="43">
-        <f>IF(AM45=1,$AG45/(1+($AF$109+메인!$A$104/10000)/2)^(AN45-1),0)</f>
+        <f>IF(AM45=1,$AG45/(1+($AF$8+메인!$A$104/10000)/2)^(AN45-1),0)</f>
         <v/>
       </c>
     </row>
@@ -10006,43 +10027,43 @@
         <v/>
       </c>
       <c r="S46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+$B$10/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+$B$10/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="T46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$96/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$96/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="U46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$97/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$97/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="V46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$98/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$98/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="W46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$99/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$99/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="X46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$100/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$100/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="Y46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$101/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$101/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="Z46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$102/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$102/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="AA46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$103/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$103/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="AB46" s="43">
-        <f>IF(I46=1,$C46/(1+($B$109+메인!$A$104/10000)/2)^(J46-1),0)</f>
+        <f>IF(I46=1,$C46/(1+($B$8+메인!$A$104/10000)/2)^(J46-1),0)</f>
         <v/>
       </c>
       <c r="AE46" s="41" t="n">
@@ -10117,43 +10138,43 @@
         <v/>
       </c>
       <c r="AW46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+$AF$10/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+$AF$10/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="AX46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$96/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$96/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="AY46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$97/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$97/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="AZ46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$98/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$98/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="BA46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$99/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$99/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="BB46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$100/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$100/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="BC46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$101/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$101/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="BD46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$102/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$102/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="BE46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$103/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$103/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
       <c r="BF46" s="43">
-        <f>IF(AM46=1,$AG46/(1+($AF$109+메인!$A$104/10000)/2)^(AN46-1),0)</f>
+        <f>IF(AM46=1,$AG46/(1+($AF$8+메인!$A$104/10000)/2)^(AN46-1),0)</f>
         <v/>
       </c>
     </row>
@@ -10230,43 +10251,43 @@
         <v/>
       </c>
       <c r="S47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+$B$10/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+$B$10/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="T47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$96/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$96/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="U47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$97/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$97/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="V47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$98/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$98/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="W47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$99/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$99/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="X47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$100/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$100/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="Y47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$101/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$101/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="Z47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$102/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$102/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="AA47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$103/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$103/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="AB47" s="43">
-        <f>IF(I47=1,$C47/(1+($B$109+메인!$A$104/10000)/2)^(J47-1),0)</f>
+        <f>IF(I47=1,$C47/(1+($B$8+메인!$A$104/10000)/2)^(J47-1),0)</f>
         <v/>
       </c>
       <c r="AE47" s="41" t="n">
@@ -10341,43 +10362,43 @@
         <v/>
       </c>
       <c r="AW47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+$AF$10/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+$AF$10/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="AX47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$96/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$96/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="AY47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$97/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$97/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="AZ47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$98/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$98/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="BA47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$99/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$99/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="BB47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$100/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$100/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="BC47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$101/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$101/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="BD47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$102/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$102/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="BE47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$103/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$103/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
       <c r="BF47" s="43">
-        <f>IF(AM47=1,$AG47/(1+($AF$109+메인!$A$104/10000)/2)^(AN47-1),0)</f>
+        <f>IF(AM47=1,$AG47/(1+($AF$8+메인!$A$104/10000)/2)^(AN47-1),0)</f>
         <v/>
       </c>
     </row>
@@ -10454,43 +10475,43 @@
         <v/>
       </c>
       <c r="S48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+$B$10/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+$B$10/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="T48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$96/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$96/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="U48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$97/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$97/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="V48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$98/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$98/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="W48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$99/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$99/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="X48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$100/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$100/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="Y48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$101/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$101/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="Z48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$102/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$102/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="AA48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$103/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$103/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="AB48" s="43">
-        <f>IF(I48=1,$C48/(1+($B$109+메인!$A$104/10000)/2)^(J48-1),0)</f>
+        <f>IF(I48=1,$C48/(1+($B$8+메인!$A$104/10000)/2)^(J48-1),0)</f>
         <v/>
       </c>
       <c r="AE48" s="41" t="n">
@@ -10565,43 +10586,43 @@
         <v/>
       </c>
       <c r="AW48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+$AF$10/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+$AF$10/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="AX48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$96/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$96/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="AY48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$97/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$97/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="AZ48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$98/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$98/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="BA48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$99/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$99/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="BB48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$100/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$100/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="BC48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$101/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$101/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="BD48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$102/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$102/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="BE48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$103/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$103/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
       <c r="BF48" s="43">
-        <f>IF(AM48=1,$AG48/(1+($AF$109+메인!$A$104/10000)/2)^(AN48-1),0)</f>
+        <f>IF(AM48=1,$AG48/(1+($AF$8+메인!$A$104/10000)/2)^(AN48-1),0)</f>
         <v/>
       </c>
     </row>
@@ -10678,43 +10699,43 @@
         <v/>
       </c>
       <c r="S49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+$B$10/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+$B$10/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="T49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$96/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$96/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="U49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$97/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$97/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="V49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$98/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$98/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="W49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$99/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$99/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="X49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$100/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$100/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="Y49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$101/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$101/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="Z49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$102/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$102/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="AA49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$103/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$103/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="AB49" s="43">
-        <f>IF(I49=1,$C49/(1+($B$109+메인!$A$104/10000)/2)^(J49-1),0)</f>
+        <f>IF(I49=1,$C49/(1+($B$8+메인!$A$104/10000)/2)^(J49-1),0)</f>
         <v/>
       </c>
       <c r="AE49" s="41" t="n">
@@ -10789,43 +10810,43 @@
         <v/>
       </c>
       <c r="AW49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+$AF$10/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+$AF$10/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="AX49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$96/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$96/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="AY49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$97/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$97/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="AZ49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$98/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$98/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="BA49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$99/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$99/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="BB49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$100/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$100/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="BC49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$101/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$101/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="BD49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$102/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$102/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="BE49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$103/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$103/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
       <c r="BF49" s="43">
-        <f>IF(AM49=1,$AG49/(1+($AF$109+메인!$A$104/10000)/2)^(AN49-1),0)</f>
+        <f>IF(AM49=1,$AG49/(1+($AF$8+메인!$A$104/10000)/2)^(AN49-1),0)</f>
         <v/>
       </c>
     </row>
@@ -10902,43 +10923,43 @@
         <v/>
       </c>
       <c r="S50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+$B$10/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+$B$10/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="T50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$96/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$96/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="U50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$97/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$97/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="V50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$98/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$98/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="W50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$99/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$99/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="X50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$100/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$100/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="Y50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$101/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$101/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="Z50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$102/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$102/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="AA50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$103/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$103/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="AB50" s="43">
-        <f>IF(I50=1,$C50/(1+($B$109+메인!$A$104/10000)/2)^(J50-1),0)</f>
+        <f>IF(I50=1,$C50/(1+($B$8+메인!$A$104/10000)/2)^(J50-1),0)</f>
         <v/>
       </c>
       <c r="AE50" s="41" t="n">
@@ -11013,43 +11034,43 @@
         <v/>
       </c>
       <c r="AW50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+$AF$10/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+$AF$10/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="AX50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$96/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$96/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="AY50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$97/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$97/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="AZ50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$98/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$98/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="BA50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$99/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$99/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="BB50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$100/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$100/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="BC50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$101/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$101/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="BD50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$102/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$102/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="BE50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$103/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$103/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
       <c r="BF50" s="43">
-        <f>IF(AM50=1,$AG50/(1+($AF$109+메인!$A$104/10000)/2)^(AN50-1),0)</f>
+        <f>IF(AM50=1,$AG50/(1+($AF$8+메인!$A$104/10000)/2)^(AN50-1),0)</f>
         <v/>
       </c>
     </row>
@@ -11126,43 +11147,43 @@
         <v/>
       </c>
       <c r="S51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+$B$10/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+$B$10/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="T51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$96/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$96/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="U51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$97/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$97/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="V51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$98/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$98/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="W51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$99/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$99/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="X51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$100/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$100/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="Y51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$101/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$101/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="Z51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$102/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$102/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="AA51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$103/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$103/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="AB51" s="43">
-        <f>IF(I51=1,$C51/(1+($B$109+메인!$A$104/10000)/2)^(J51-1),0)</f>
+        <f>IF(I51=1,$C51/(1+($B$8+메인!$A$104/10000)/2)^(J51-1),0)</f>
         <v/>
       </c>
       <c r="AE51" s="41" t="n">
@@ -11237,43 +11258,43 @@
         <v/>
       </c>
       <c r="AW51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+$AF$10/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+$AF$10/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="AX51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$96/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$96/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="AY51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$97/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$97/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="AZ51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$98/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$98/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="BA51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$99/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$99/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="BB51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$100/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$100/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="BC51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$101/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$101/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="BD51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$102/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$102/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="BE51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$103/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$103/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
       <c r="BF51" s="43">
-        <f>IF(AM51=1,$AG51/(1+($AF$109+메인!$A$104/10000)/2)^(AN51-1),0)</f>
+        <f>IF(AM51=1,$AG51/(1+($AF$8+메인!$A$104/10000)/2)^(AN51-1),0)</f>
         <v/>
       </c>
     </row>
@@ -11350,43 +11371,43 @@
         <v/>
       </c>
       <c r="S52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+$B$10/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+$B$10/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="T52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$96/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$96/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="U52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$97/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$97/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="V52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$98/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$98/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="W52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$99/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$99/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="X52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$100/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$100/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="Y52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$101/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$101/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="Z52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$102/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$102/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="AA52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$103/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$103/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="AB52" s="43">
-        <f>IF(I52=1,$C52/(1+($B$109+메인!$A$104/10000)/2)^(J52-1),0)</f>
+        <f>IF(I52=1,$C52/(1+($B$8+메인!$A$104/10000)/2)^(J52-1),0)</f>
         <v/>
       </c>
       <c r="AE52" s="41" t="n">
@@ -11461,43 +11482,43 @@
         <v/>
       </c>
       <c r="AW52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+$AF$10/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+$AF$10/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="AX52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$96/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$96/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="AY52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$97/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$97/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="AZ52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$98/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$98/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="BA52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$99/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$99/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="BB52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$100/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$100/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="BC52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$101/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$101/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="BD52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$102/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$102/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="BE52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$103/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$103/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
       <c r="BF52" s="43">
-        <f>IF(AM52=1,$AG52/(1+($AF$109+메인!$A$104/10000)/2)^(AN52-1),0)</f>
+        <f>IF(AM52=1,$AG52/(1+($AF$8+메인!$A$104/10000)/2)^(AN52-1),0)</f>
         <v/>
       </c>
     </row>
@@ -11574,43 +11595,43 @@
         <v/>
       </c>
       <c r="S53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+$B$10/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+$B$10/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="T53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$96/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$96/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="U53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$97/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$97/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="V53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$98/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$98/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="W53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$99/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$99/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="X53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$100/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$100/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="Y53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$101/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$101/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="Z53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$102/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$102/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="AA53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$103/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$103/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="AB53" s="43">
-        <f>IF(I53=1,$C53/(1+($B$109+메인!$A$104/10000)/2)^(J53-1),0)</f>
+        <f>IF(I53=1,$C53/(1+($B$8+메인!$A$104/10000)/2)^(J53-1),0)</f>
         <v/>
       </c>
       <c r="AE53" s="41" t="n">
@@ -11685,43 +11706,43 @@
         <v/>
       </c>
       <c r="AW53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+$AF$10/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+$AF$10/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="AX53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$96/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$96/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="AY53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$97/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$97/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="AZ53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$98/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$98/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="BA53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$99/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$99/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="BB53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$100/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$100/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="BC53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$101/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$101/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="BD53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$102/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$102/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="BE53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$103/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$103/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
       <c r="BF53" s="43">
-        <f>IF(AM53=1,$AG53/(1+($AF$109+메인!$A$104/10000)/2)^(AN53-1),0)</f>
+        <f>IF(AM53=1,$AG53/(1+($AF$8+메인!$A$104/10000)/2)^(AN53-1),0)</f>
         <v/>
       </c>
     </row>
@@ -11798,43 +11819,43 @@
         <v/>
       </c>
       <c r="S54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+$B$10/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+$B$10/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="T54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$96/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$96/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="U54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$97/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$97/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="V54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$98/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$98/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="W54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$99/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$99/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="X54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$100/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$100/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="Y54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$101/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$101/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="Z54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$102/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$102/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="AA54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$103/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$103/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="AB54" s="43">
-        <f>IF(I54=1,$C54/(1+($B$109+메인!$A$104/10000)/2)^(J54-1),0)</f>
+        <f>IF(I54=1,$C54/(1+($B$8+메인!$A$104/10000)/2)^(J54-1),0)</f>
         <v/>
       </c>
       <c r="AE54" s="41" t="n">
@@ -11909,43 +11930,43 @@
         <v/>
       </c>
       <c r="AW54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+$AF$10/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+$AF$10/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="AX54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$96/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$96/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="AY54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$97/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$97/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="AZ54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$98/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$98/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="BA54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$99/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$99/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="BB54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$100/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$100/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="BC54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$101/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$101/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="BD54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$102/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$102/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="BE54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$103/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$103/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
       <c r="BF54" s="43">
-        <f>IF(AM54=1,$AG54/(1+($AF$109+메인!$A$104/10000)/2)^(AN54-1),0)</f>
+        <f>IF(AM54=1,$AG54/(1+($AF$8+메인!$A$104/10000)/2)^(AN54-1),0)</f>
         <v/>
       </c>
     </row>
@@ -12022,43 +12043,43 @@
         <v/>
       </c>
       <c r="S55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+$B$10/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+$B$10/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="T55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$96/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$96/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="U55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$97/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$97/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="V55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$98/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$98/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="W55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$99/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$99/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="X55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$100/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$100/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="Y55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$101/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$101/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="Z55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$102/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$102/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="AA55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$103/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$103/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="AB55" s="43">
-        <f>IF(I55=1,$C55/(1+($B$109+메인!$A$104/10000)/2)^(J55-1),0)</f>
+        <f>IF(I55=1,$C55/(1+($B$8+메인!$A$104/10000)/2)^(J55-1),0)</f>
         <v/>
       </c>
       <c r="AE55" s="41" t="n">
@@ -12133,43 +12154,43 @@
         <v/>
       </c>
       <c r="AW55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+$AF$10/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+$AF$10/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="AX55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$96/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$96/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="AY55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$97/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$97/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="AZ55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$98/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$98/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="BA55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$99/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$99/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="BB55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$100/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$100/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="BC55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$101/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$101/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="BD55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$102/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$102/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="BE55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$103/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$103/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
       <c r="BF55" s="43">
-        <f>IF(AM55=1,$AG55/(1+($AF$109+메인!$A$104/10000)/2)^(AN55-1),0)</f>
+        <f>IF(AM55=1,$AG55/(1+($AF$8+메인!$A$104/10000)/2)^(AN55-1),0)</f>
         <v/>
       </c>
     </row>
@@ -12246,43 +12267,43 @@
         <v/>
       </c>
       <c r="S56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+$B$10/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+$B$10/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="T56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$96/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$96/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="U56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$97/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$97/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="V56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$98/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$98/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="W56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$99/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$99/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="X56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$100/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$100/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="Y56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$101/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$101/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="Z56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$102/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$102/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="AA56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$103/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$103/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="AB56" s="43">
-        <f>IF(I56=1,$C56/(1+($B$109+메인!$A$104/10000)/2)^(J56-1),0)</f>
+        <f>IF(I56=1,$C56/(1+($B$8+메인!$A$104/10000)/2)^(J56-1),0)</f>
         <v/>
       </c>
       <c r="AE56" s="41" t="n">
@@ -12357,43 +12378,43 @@
         <v/>
       </c>
       <c r="AW56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+$AF$10/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+$AF$10/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="AX56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$96/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$96/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="AY56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$97/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$97/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="AZ56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$98/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$98/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="BA56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$99/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$99/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="BB56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$100/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$100/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="BC56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$101/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$101/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="BD56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$102/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$102/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="BE56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$103/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$103/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
       <c r="BF56" s="43">
-        <f>IF(AM56=1,$AG56/(1+($AF$109+메인!$A$104/10000)/2)^(AN56-1),0)</f>
+        <f>IF(AM56=1,$AG56/(1+($AF$8+메인!$A$104/10000)/2)^(AN56-1),0)</f>
         <v/>
       </c>
     </row>
@@ -12470,43 +12491,43 @@
         <v/>
       </c>
       <c r="S57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+$B$10/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+$B$10/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="T57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$96/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$96/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="U57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$97/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$97/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="V57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$98/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$98/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="W57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$99/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$99/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="X57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$100/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$100/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="Y57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$101/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$101/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="Z57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$102/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$102/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="AA57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$103/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$103/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="AB57" s="43">
-        <f>IF(I57=1,$C57/(1+($B$109+메인!$A$104/10000)/2)^(J57-1),0)</f>
+        <f>IF(I57=1,$C57/(1+($B$8+메인!$A$104/10000)/2)^(J57-1),0)</f>
         <v/>
       </c>
       <c r="AE57" s="41" t="n">
@@ -12581,43 +12602,43 @@
         <v/>
       </c>
       <c r="AW57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+$AF$10/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+$AF$10/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="AX57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$96/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$96/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="AY57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$97/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$97/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="AZ57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$98/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$98/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="BA57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$99/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$99/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="BB57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$100/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$100/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="BC57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$101/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$101/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="BD57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$102/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$102/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="BE57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$103/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$103/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
       <c r="BF57" s="43">
-        <f>IF(AM57=1,$AG57/(1+($AF$109+메인!$A$104/10000)/2)^(AN57-1),0)</f>
+        <f>IF(AM57=1,$AG57/(1+($AF$8+메인!$A$104/10000)/2)^(AN57-1),0)</f>
         <v/>
       </c>
     </row>
@@ -12694,43 +12715,43 @@
         <v/>
       </c>
       <c r="S58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+$B$10/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+$B$10/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="T58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$96/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$96/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="U58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$97/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$97/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="V58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$98/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$98/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="W58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$99/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$99/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="X58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$100/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$100/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="Y58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$101/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$101/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="Z58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$102/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$102/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="AA58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$103/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$103/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="AB58" s="43">
-        <f>IF(I58=1,$C58/(1+($B$109+메인!$A$104/10000)/2)^(J58-1),0)</f>
+        <f>IF(I58=1,$C58/(1+($B$8+메인!$A$104/10000)/2)^(J58-1),0)</f>
         <v/>
       </c>
       <c r="AE58" s="41" t="n">
@@ -12805,43 +12826,43 @@
         <v/>
       </c>
       <c r="AW58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+$AF$10/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+$AF$10/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="AX58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$96/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$96/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="AY58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$97/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$97/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="AZ58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$98/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$98/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="BA58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$99/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$99/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="BB58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$100/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$100/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="BC58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$101/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$101/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="BD58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$102/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$102/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="BE58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$103/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$103/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
       <c r="BF58" s="43">
-        <f>IF(AM58=1,$AG58/(1+($AF$109+메인!$A$104/10000)/2)^(AN58-1),0)</f>
+        <f>IF(AM58=1,$AG58/(1+($AF$8+메인!$A$104/10000)/2)^(AN58-1),0)</f>
         <v/>
       </c>
     </row>
@@ -12918,43 +12939,43 @@
         <v/>
       </c>
       <c r="S59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+$B$10/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+$B$10/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="T59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$96/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$96/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="U59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$97/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$97/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="V59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$98/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$98/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="W59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$99/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$99/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="X59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$100/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$100/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="Y59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$101/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$101/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="Z59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$102/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$102/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="AA59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$103/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$103/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="AB59" s="43">
-        <f>IF(I59=1,$C59/(1+($B$109+메인!$A$104/10000)/2)^(J59-1),0)</f>
+        <f>IF(I59=1,$C59/(1+($B$8+메인!$A$104/10000)/2)^(J59-1),0)</f>
         <v/>
       </c>
       <c r="AE59" s="41" t="n">
@@ -13029,43 +13050,43 @@
         <v/>
       </c>
       <c r="AW59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+$AF$10/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+$AF$10/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="AX59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$96/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$96/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="AY59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$97/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$97/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="AZ59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$98/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$98/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="BA59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$99/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$99/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="BB59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$100/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$100/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="BC59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$101/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$101/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="BD59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$102/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$102/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="BE59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$103/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$103/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
       <c r="BF59" s="43">
-        <f>IF(AM59=1,$AG59/(1+($AF$109+메인!$A$104/10000)/2)^(AN59-1),0)</f>
+        <f>IF(AM59=1,$AG59/(1+($AF$8+메인!$A$104/10000)/2)^(AN59-1),0)</f>
         <v/>
       </c>
     </row>
@@ -13142,43 +13163,43 @@
         <v/>
       </c>
       <c r="S60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+$B$10/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+$B$10/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="T60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$96/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$96/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="U60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$97/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$97/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="V60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$98/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$98/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="W60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$99/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$99/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="X60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$100/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$100/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="Y60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$101/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$101/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="Z60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$102/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$102/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="AA60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$103/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$103/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="AB60" s="43">
-        <f>IF(I60=1,$C60/(1+($B$109+메인!$A$104/10000)/2)^(J60-1),0)</f>
+        <f>IF(I60=1,$C60/(1+($B$8+메인!$A$104/10000)/2)^(J60-1),0)</f>
         <v/>
       </c>
       <c r="AE60" s="41" t="n">
@@ -13253,43 +13274,43 @@
         <v/>
       </c>
       <c r="AW60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+$AF$10/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+$AF$10/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="AX60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$96/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$96/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="AY60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$97/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$97/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="AZ60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$98/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$98/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="BA60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$99/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$99/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="BB60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$100/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$100/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="BC60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$101/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$101/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="BD60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$102/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$102/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="BE60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$103/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$103/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
       <c r="BF60" s="43">
-        <f>IF(AM60=1,$AG60/(1+($AF$109+메인!$A$104/10000)/2)^(AN60-1),0)</f>
+        <f>IF(AM60=1,$AG60/(1+($AF$8+메인!$A$104/10000)/2)^(AN60-1),0)</f>
         <v/>
       </c>
     </row>
@@ -13366,43 +13387,43 @@
         <v/>
       </c>
       <c r="S61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+$B$10/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+$B$10/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="T61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$96/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$96/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="U61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$97/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$97/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="V61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$98/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$98/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="W61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$99/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$99/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="X61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$100/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$100/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="Y61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$101/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$101/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="Z61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$102/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$102/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="AA61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$103/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$103/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="AB61" s="43">
-        <f>IF(I61=1,$C61/(1+($B$109+메인!$A$104/10000)/2)^(J61-1),0)</f>
+        <f>IF(I61=1,$C61/(1+($B$8+메인!$A$104/10000)/2)^(J61-1),0)</f>
         <v/>
       </c>
       <c r="AE61" s="41" t="n">
@@ -13477,43 +13498,43 @@
         <v/>
       </c>
       <c r="AW61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+$AF$10/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+$AF$10/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="AX61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$96/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$96/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="AY61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$97/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$97/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="AZ61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$98/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$98/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="BA61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$99/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$99/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="BB61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$100/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$100/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="BC61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$101/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$101/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="BD61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$102/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$102/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="BE61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$103/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$103/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
       <c r="BF61" s="43">
-        <f>IF(AM61=1,$AG61/(1+($AF$109+메인!$A$104/10000)/2)^(AN61-1),0)</f>
+        <f>IF(AM61=1,$AG61/(1+($AF$8+메인!$A$104/10000)/2)^(AN61-1),0)</f>
         <v/>
       </c>
     </row>
@@ -13590,43 +13611,43 @@
         <v/>
       </c>
       <c r="S62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+$B$10/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+$B$10/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="T62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$96/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$96/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="U62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$97/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$97/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="V62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$98/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$98/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="W62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$99/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$99/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="X62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$100/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$100/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="Y62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$101/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$101/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="Z62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$102/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$102/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="AA62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$103/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$103/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="AB62" s="43">
-        <f>IF(I62=1,$C62/(1+($B$109+메인!$A$104/10000)/2)^(J62-1),0)</f>
+        <f>IF(I62=1,$C62/(1+($B$8+메인!$A$104/10000)/2)^(J62-1),0)</f>
         <v/>
       </c>
       <c r="AE62" s="41" t="n">
@@ -13701,43 +13722,43 @@
         <v/>
       </c>
       <c r="AW62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+$AF$10/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+$AF$10/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="AX62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$96/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$96/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="AY62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$97/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$97/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="AZ62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$98/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$98/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="BA62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$99/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$99/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="BB62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$100/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$100/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="BC62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$101/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$101/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="BD62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$102/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$102/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="BE62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$103/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$103/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
       <c r="BF62" s="43">
-        <f>IF(AM62=1,$AG62/(1+($AF$109+메인!$A$104/10000)/2)^(AN62-1),0)</f>
+        <f>IF(AM62=1,$AG62/(1+($AF$8+메인!$A$104/10000)/2)^(AN62-1),0)</f>
         <v/>
       </c>
     </row>
@@ -13814,43 +13835,43 @@
         <v/>
       </c>
       <c r="S63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+$B$10/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+$B$10/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="T63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$96/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$96/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="U63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$97/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$97/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="V63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$98/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$98/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="W63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$99/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$99/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="X63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$100/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$100/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="Y63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$101/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$101/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="Z63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$102/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$102/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="AA63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$103/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$103/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="AB63" s="43">
-        <f>IF(I63=1,$C63/(1+($B$109+메인!$A$104/10000)/2)^(J63-1),0)</f>
+        <f>IF(I63=1,$C63/(1+($B$8+메인!$A$104/10000)/2)^(J63-1),0)</f>
         <v/>
       </c>
       <c r="AE63" s="41" t="n">
@@ -13925,43 +13946,43 @@
         <v/>
       </c>
       <c r="AW63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+$AF$10/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+$AF$10/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="AX63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$96/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$96/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="AY63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$97/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$97/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="AZ63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$98/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$98/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="BA63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$99/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$99/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="BB63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$100/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$100/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="BC63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$101/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$101/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="BD63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$102/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$102/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="BE63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$103/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$103/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
       <c r="BF63" s="43">
-        <f>IF(AM63=1,$AG63/(1+($AF$109+메인!$A$104/10000)/2)^(AN63-1),0)</f>
+        <f>IF(AM63=1,$AG63/(1+($AF$8+메인!$A$104/10000)/2)^(AN63-1),0)</f>
         <v/>
       </c>
     </row>
@@ -14038,43 +14059,43 @@
         <v/>
       </c>
       <c r="S64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+$B$10/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+$B$10/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="T64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$96/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$96/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="U64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$97/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$97/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="V64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$98/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$98/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="W64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$99/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$99/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="X64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$100/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$100/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="Y64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$101/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$101/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="Z64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$102/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$102/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="AA64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$103/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$103/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="AB64" s="43">
-        <f>IF(I64=1,$C64/(1+($B$109+메인!$A$104/10000)/2)^(J64-1),0)</f>
+        <f>IF(I64=1,$C64/(1+($B$8+메인!$A$104/10000)/2)^(J64-1),0)</f>
         <v/>
       </c>
       <c r="AE64" s="41" t="n">
@@ -14149,43 +14170,43 @@
         <v/>
       </c>
       <c r="AW64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+$AF$10/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+$AF$10/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="AX64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$96/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$96/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="AY64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$97/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$97/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="AZ64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$98/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$98/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="BA64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$99/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$99/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="BB64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$100/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$100/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="BC64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$101/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$101/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="BD64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$102/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$102/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="BE64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$103/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$103/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
       <c r="BF64" s="43">
-        <f>IF(AM64=1,$AG64/(1+($AF$109+메인!$A$104/10000)/2)^(AN64-1),0)</f>
+        <f>IF(AM64=1,$AG64/(1+($AF$8+메인!$A$104/10000)/2)^(AN64-1),0)</f>
         <v/>
       </c>
     </row>
@@ -14262,43 +14283,43 @@
         <v/>
       </c>
       <c r="S65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+$B$10/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+$B$10/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="T65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$96/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$96/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="U65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$97/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$97/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="V65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$98/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$98/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="W65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$99/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$99/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="X65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$100/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$100/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="Y65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$101/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$101/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="Z65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$102/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$102/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="AA65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$103/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$103/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="AB65" s="43">
-        <f>IF(I65=1,$C65/(1+($B$109+메인!$A$104/10000)/2)^(J65-1),0)</f>
+        <f>IF(I65=1,$C65/(1+($B$8+메인!$A$104/10000)/2)^(J65-1),0)</f>
         <v/>
       </c>
       <c r="AE65" s="41" t="n">
@@ -14373,43 +14394,43 @@
         <v/>
       </c>
       <c r="AW65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+$AF$10/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+$AF$10/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="AX65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$96/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$96/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="AY65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$97/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$97/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="AZ65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$98/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$98/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="BA65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$99/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$99/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="BB65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$100/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$100/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="BC65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$101/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$101/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="BD65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$102/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$102/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="BE65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$103/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$103/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
       <c r="BF65" s="43">
-        <f>IF(AM65=1,$AG65/(1+($AF$109+메인!$A$104/10000)/2)^(AN65-1),0)</f>
+        <f>IF(AM65=1,$AG65/(1+($AF$8+메인!$A$104/10000)/2)^(AN65-1),0)</f>
         <v/>
       </c>
     </row>
@@ -14486,43 +14507,43 @@
         <v/>
       </c>
       <c r="S66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+$B$10/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+$B$10/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="T66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$96/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$96/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="U66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$97/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$97/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="V66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$98/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$98/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="W66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$99/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$99/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="X66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$100/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$100/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="Y66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$101/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$101/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="Z66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$102/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$102/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="AA66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$103/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$103/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="AB66" s="43">
-        <f>IF(I66=1,$C66/(1+($B$109+메인!$A$104/10000)/2)^(J66-1),0)</f>
+        <f>IF(I66=1,$C66/(1+($B$8+메인!$A$104/10000)/2)^(J66-1),0)</f>
         <v/>
       </c>
       <c r="AE66" s="41" t="n">
@@ -14597,43 +14618,43 @@
         <v/>
       </c>
       <c r="AW66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+$AF$10/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+$AF$10/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="AX66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$96/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$96/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="AY66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$97/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$97/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="AZ66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$98/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$98/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="BA66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$99/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$99/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="BB66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$100/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$100/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="BC66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$101/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$101/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="BD66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$102/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$102/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="BE66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$103/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$103/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
       <c r="BF66" s="43">
-        <f>IF(AM66=1,$AG66/(1+($AF$109+메인!$A$104/10000)/2)^(AN66-1),0)</f>
+        <f>IF(AM66=1,$AG66/(1+($AF$8+메인!$A$104/10000)/2)^(AN66-1),0)</f>
         <v/>
       </c>
     </row>
@@ -14710,43 +14731,43 @@
         <v/>
       </c>
       <c r="S67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+$B$10/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+$B$10/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="T67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$96/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$96/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="U67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$97/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$97/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="V67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$98/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$98/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="W67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$99/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$99/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="X67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$100/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$100/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="Y67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$101/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$101/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="Z67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$102/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$102/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="AA67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$103/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$103/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="AB67" s="43">
-        <f>IF(I67=1,$C67/(1+($B$109+메인!$A$104/10000)/2)^(J67-1),0)</f>
+        <f>IF(I67=1,$C67/(1+($B$8+메인!$A$104/10000)/2)^(J67-1),0)</f>
         <v/>
       </c>
       <c r="AE67" s="41" t="n">
@@ -14821,43 +14842,43 @@
         <v/>
       </c>
       <c r="AW67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+$AF$10/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+$AF$10/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="AX67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$96/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$96/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="AY67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$97/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$97/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="AZ67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$98/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$98/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="BA67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$99/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$99/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="BB67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$100/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$100/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="BC67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$101/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$101/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="BD67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$102/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$102/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="BE67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$103/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$103/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
       <c r="BF67" s="43">
-        <f>IF(AM67=1,$AG67/(1+($AF$109+메인!$A$104/10000)/2)^(AN67-1),0)</f>
+        <f>IF(AM67=1,$AG67/(1+($AF$8+메인!$A$104/10000)/2)^(AN67-1),0)</f>
         <v/>
       </c>
     </row>
@@ -14934,43 +14955,43 @@
         <v/>
       </c>
       <c r="S68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+$B$10/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+$B$10/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="T68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$96/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$96/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="U68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$97/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$97/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="V68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$98/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$98/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="W68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$99/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$99/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="X68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$100/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$100/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="Y68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$101/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$101/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="Z68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$102/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$102/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="AA68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$103/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$103/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="AB68" s="43">
-        <f>IF(I68=1,$C68/(1+($B$109+메인!$A$104/10000)/2)^(J68-1),0)</f>
+        <f>IF(I68=1,$C68/(1+($B$8+메인!$A$104/10000)/2)^(J68-1),0)</f>
         <v/>
       </c>
       <c r="AE68" s="41" t="n">
@@ -15045,43 +15066,43 @@
         <v/>
       </c>
       <c r="AW68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+$AF$10/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+$AF$10/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="AX68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$96/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$96/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="AY68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$97/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$97/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="AZ68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$98/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$98/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="BA68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$99/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$99/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="BB68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$100/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$100/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="BC68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$101/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$101/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="BD68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$102/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$102/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="BE68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$103/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$103/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
       <c r="BF68" s="43">
-        <f>IF(AM68=1,$AG68/(1+($AF$109+메인!$A$104/10000)/2)^(AN68-1),0)</f>
+        <f>IF(AM68=1,$AG68/(1+($AF$8+메인!$A$104/10000)/2)^(AN68-1),0)</f>
         <v/>
       </c>
     </row>
@@ -15158,43 +15179,43 @@
         <v/>
       </c>
       <c r="S69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+$B$10/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+$B$10/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="T69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$96/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$96/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="U69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$97/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$97/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="V69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$98/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$98/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="W69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$99/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$99/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="X69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$100/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$100/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="Y69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$101/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$101/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="Z69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$102/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$102/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="AA69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$103/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$103/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="AB69" s="43">
-        <f>IF(I69=1,$C69/(1+($B$109+메인!$A$104/10000)/2)^(J69-1),0)</f>
+        <f>IF(I69=1,$C69/(1+($B$8+메인!$A$104/10000)/2)^(J69-1),0)</f>
         <v/>
       </c>
       <c r="AE69" s="41" t="n">
@@ -15269,43 +15290,43 @@
         <v/>
       </c>
       <c r="AW69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+$AF$10/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+$AF$10/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="AX69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$96/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$96/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="AY69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$97/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$97/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="AZ69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$98/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$98/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="BA69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$99/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$99/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="BB69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$100/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$100/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="BC69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$101/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$101/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="BD69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$102/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$102/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="BE69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$103/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$103/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
       <c r="BF69" s="43">
-        <f>IF(AM69=1,$AG69/(1+($AF$109+메인!$A$104/10000)/2)^(AN69-1),0)</f>
+        <f>IF(AM69=1,$AG69/(1+($AF$8+메인!$A$104/10000)/2)^(AN69-1),0)</f>
         <v/>
       </c>
     </row>
@@ -15382,43 +15403,43 @@
         <v/>
       </c>
       <c r="S70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+$B$10/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+$B$10/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="T70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$96/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$96/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="U70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$97/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$97/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="V70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$98/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$98/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="W70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$99/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$99/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="X70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$100/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$100/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="Y70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$101/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$101/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="Z70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$102/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$102/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="AA70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$103/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$103/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="AB70" s="43">
-        <f>IF(I70=1,$C70/(1+($B$109+메인!$A$104/10000)/2)^(J70-1),0)</f>
+        <f>IF(I70=1,$C70/(1+($B$8+메인!$A$104/10000)/2)^(J70-1),0)</f>
         <v/>
       </c>
       <c r="AE70" s="41" t="n">
@@ -15493,43 +15514,43 @@
         <v/>
       </c>
       <c r="AW70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+$AF$10/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+$AF$10/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="AX70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$96/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$96/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="AY70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$97/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$97/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="AZ70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$98/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$98/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="BA70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$99/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$99/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="BB70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$100/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$100/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="BC70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$101/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$101/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="BD70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$102/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$102/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="BE70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$103/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$103/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
       <c r="BF70" s="43">
-        <f>IF(AM70=1,$AG70/(1+($AF$109+메인!$A$104/10000)/2)^(AN70-1),0)</f>
+        <f>IF(AM70=1,$AG70/(1+($AF$8+메인!$A$104/10000)/2)^(AN70-1),0)</f>
         <v/>
       </c>
     </row>
@@ -15606,43 +15627,43 @@
         <v/>
       </c>
       <c r="S71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+$B$10/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+$B$10/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="T71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$96/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$96/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="U71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$97/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$97/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="V71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$98/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$98/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="W71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$99/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$99/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="X71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$100/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$100/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="Y71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$101/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$101/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="Z71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$102/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$102/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="AA71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$103/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$103/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="AB71" s="43">
-        <f>IF(I71=1,$C71/(1+($B$109+메인!$A$104/10000)/2)^(J71-1),0)</f>
+        <f>IF(I71=1,$C71/(1+($B$8+메인!$A$104/10000)/2)^(J71-1),0)</f>
         <v/>
       </c>
       <c r="AE71" s="41" t="n">
@@ -15717,43 +15738,43 @@
         <v/>
       </c>
       <c r="AW71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+$AF$10/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+$AF$10/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="AX71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$96/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$96/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="AY71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$97/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$97/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="AZ71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$98/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$98/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="BA71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$99/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$99/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="BB71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$100/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$100/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="BC71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$101/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$101/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="BD71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$102/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$102/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="BE71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$103/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$103/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
       <c r="BF71" s="43">
-        <f>IF(AM71=1,$AG71/(1+($AF$109+메인!$A$104/10000)/2)^(AN71-1),0)</f>
+        <f>IF(AM71=1,$AG71/(1+($AF$8+메인!$A$104/10000)/2)^(AN71-1),0)</f>
         <v/>
       </c>
     </row>
@@ -15830,43 +15851,43 @@
         <v/>
       </c>
       <c r="S72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+$B$10/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+$B$10/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="T72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$96/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$96/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="U72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$97/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$97/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="V72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$98/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$98/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="W72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$99/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$99/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="X72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$100/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$100/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="Y72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$101/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$101/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="Z72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$102/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$102/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="AA72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$103/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$103/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="AB72" s="43">
-        <f>IF(I72=1,$C72/(1+($B$109+메인!$A$104/10000)/2)^(J72-1),0)</f>
+        <f>IF(I72=1,$C72/(1+($B$8+메인!$A$104/10000)/2)^(J72-1),0)</f>
         <v/>
       </c>
       <c r="AE72" s="41" t="n">
@@ -15941,43 +15962,43 @@
         <v/>
       </c>
       <c r="AW72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+$AF$10/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+$AF$10/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="AX72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$96/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$96/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="AY72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$97/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$97/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="AZ72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$98/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$98/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="BA72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$99/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$99/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="BB72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$100/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$100/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="BC72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$101/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$101/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="BD72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$102/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$102/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="BE72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$103/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$103/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
       <c r="BF72" s="43">
-        <f>IF(AM72=1,$AG72/(1+($AF$109+메인!$A$104/10000)/2)^(AN72-1),0)</f>
+        <f>IF(AM72=1,$AG72/(1+($AF$8+메인!$A$104/10000)/2)^(AN72-1),0)</f>
         <v/>
       </c>
     </row>
@@ -16054,43 +16075,43 @@
         <v/>
       </c>
       <c r="S73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+$B$10/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+$B$10/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="T73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$96/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$96/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="U73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$97/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$97/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="V73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$98/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$98/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="W73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$99/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$99/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="X73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$100/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$100/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="Y73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$101/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$101/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="Z73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$102/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$102/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="AA73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$103/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$103/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="AB73" s="43">
-        <f>IF(I73=1,$C73/(1+($B$109+메인!$A$104/10000)/2)^(J73-1),0)</f>
+        <f>IF(I73=1,$C73/(1+($B$8+메인!$A$104/10000)/2)^(J73-1),0)</f>
         <v/>
       </c>
       <c r="AE73" s="41" t="n">
@@ -16165,43 +16186,43 @@
         <v/>
       </c>
       <c r="AW73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+$AF$10/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+$AF$10/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="AX73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$96/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$96/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="AY73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$97/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$97/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="AZ73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$98/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$98/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="BA73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$99/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$99/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="BB73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$100/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$100/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="BC73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$101/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$101/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="BD73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$102/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$102/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="BE73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$103/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$103/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
       <c r="BF73" s="43">
-        <f>IF(AM73=1,$AG73/(1+($AF$109+메인!$A$104/10000)/2)^(AN73-1),0)</f>
+        <f>IF(AM73=1,$AG73/(1+($AF$8+메인!$A$104/10000)/2)^(AN73-1),0)</f>
         <v/>
       </c>
     </row>
@@ -16278,43 +16299,43 @@
         <v/>
       </c>
       <c r="S74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+$B$10/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+$B$10/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="T74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$96/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$96/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="U74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$97/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$97/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="V74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$98/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$98/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="W74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$99/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$99/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="X74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$100/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$100/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="Y74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$101/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$101/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="Z74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$102/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$102/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="AA74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$103/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$103/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="AB74" s="43">
-        <f>IF(I74=1,$C74/(1+($B$109+메인!$A$104/10000)/2)^(J74-1),0)</f>
+        <f>IF(I74=1,$C74/(1+($B$8+메인!$A$104/10000)/2)^(J74-1),0)</f>
         <v/>
       </c>
       <c r="AE74" s="41" t="n">
@@ -16389,43 +16410,43 @@
         <v/>
       </c>
       <c r="AW74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+$AF$10/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+$AF$10/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="AX74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$96/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$96/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="AY74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$97/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$97/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="AZ74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$98/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$98/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="BA74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$99/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$99/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="BB74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$100/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$100/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="BC74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$101/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$101/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="BD74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$102/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$102/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="BE74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$103/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$103/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
       <c r="BF74" s="43">
-        <f>IF(AM74=1,$AG74/(1+($AF$109+메인!$A$104/10000)/2)^(AN74-1),0)</f>
+        <f>IF(AM74=1,$AG74/(1+($AF$8+메인!$A$104/10000)/2)^(AN74-1),0)</f>
         <v/>
       </c>
     </row>
@@ -16502,43 +16523,43 @@
         <v/>
       </c>
       <c r="S75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+$B$10/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+$B$10/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="T75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$96/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$96/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="U75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$97/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$97/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="V75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$98/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$98/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="W75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$99/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$99/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="X75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$100/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$100/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="Y75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$101/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$101/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="Z75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$102/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$102/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="AA75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$103/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$103/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="AB75" s="43">
-        <f>IF(I75=1,$C75/(1+($B$109+메인!$A$104/10000)/2)^(J75-1),0)</f>
+        <f>IF(I75=1,$C75/(1+($B$8+메인!$A$104/10000)/2)^(J75-1),0)</f>
         <v/>
       </c>
       <c r="AE75" s="41" t="n">
@@ -16613,43 +16634,43 @@
         <v/>
       </c>
       <c r="AW75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+$AF$10/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+$AF$10/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="AX75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$96/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$96/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="AY75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$97/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$97/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="AZ75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$98/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$98/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="BA75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$99/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$99/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="BB75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$100/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$100/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="BC75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$101/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$101/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="BD75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$102/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$102/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="BE75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$103/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$103/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
       <c r="BF75" s="43">
-        <f>IF(AM75=1,$AG75/(1+($AF$109+메인!$A$104/10000)/2)^(AN75-1),0)</f>
+        <f>IF(AM75=1,$AG75/(1+($AF$8+메인!$A$104/10000)/2)^(AN75-1),0)</f>
         <v/>
       </c>
     </row>
@@ -16726,43 +16747,43 @@
         <v/>
       </c>
       <c r="S76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+$B$10/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+$B$10/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="T76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$96/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$96/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="U76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$97/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$97/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="V76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$98/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$98/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="W76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$99/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$99/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="X76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$100/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$100/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="Y76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$101/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$101/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="Z76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$102/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$102/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="AA76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$103/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$103/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="AB76" s="43">
-        <f>IF(I76=1,$C76/(1+($B$109+메인!$A$104/10000)/2)^(J76-1),0)</f>
+        <f>IF(I76=1,$C76/(1+($B$8+메인!$A$104/10000)/2)^(J76-1),0)</f>
         <v/>
       </c>
       <c r="AE76" s="41" t="n">
@@ -16837,43 +16858,43 @@
         <v/>
       </c>
       <c r="AW76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+$AF$10/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+$AF$10/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="AX76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$96/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$96/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="AY76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$97/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$97/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="AZ76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$98/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$98/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="BA76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$99/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$99/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="BB76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$100/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$100/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="BC76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$101/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$101/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="BD76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$102/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$102/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="BE76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$103/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$103/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
       <c r="BF76" s="43">
-        <f>IF(AM76=1,$AG76/(1+($AF$109+메인!$A$104/10000)/2)^(AN76-1),0)</f>
+        <f>IF(AM76=1,$AG76/(1+($AF$8+메인!$A$104/10000)/2)^(AN76-1),0)</f>
         <v/>
       </c>
     </row>
@@ -17540,7 +17561,7 @@
         </is>
       </c>
       <c r="B114" s="24">
-        <f>SUM(S15:S76)/(1+(B109+$B$10/10000)/2*B93/B94)</f>
+        <f>SUM(S15:S76)/(1+(B8+$B$10/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE114" s="5" t="inlineStr">
@@ -17549,7 +17570,7 @@
         </is>
       </c>
       <c r="AF114" s="24">
-        <f>SUM(AW15:AW76)/(1+(AF109+$AF$10/10000)/2*AF93/AF94)</f>
+        <f>SUM(AW15:AW76)/(1+(AF8+$AF$10/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17560,7 +17581,7 @@
         </is>
       </c>
       <c r="B115" s="24">
-        <f>SUM(T15:T76)/(1+(B109+메인!$A$96/10000)/2*B93/B94)</f>
+        <f>SUM(T15:T76)/(1+(B8+메인!$A$96/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE115" s="5" t="inlineStr">
@@ -17569,7 +17590,7 @@
         </is>
       </c>
       <c r="AF115" s="24">
-        <f>SUM(AX15:AX76)/(1+(AF109+메인!$A$96/10000)/2*AF93/AF94)</f>
+        <f>SUM(AX15:AX76)/(1+(AF8+메인!$A$96/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17580,7 +17601,7 @@
         </is>
       </c>
       <c r="B116" s="24">
-        <f>SUM(U15:U76)/(1+(B109+메인!$A$97/10000)/2*B93/B94)</f>
+        <f>SUM(U15:U76)/(1+(B8+메인!$A$97/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE116" s="5" t="inlineStr">
@@ -17589,7 +17610,7 @@
         </is>
       </c>
       <c r="AF116" s="24">
-        <f>SUM(AY15:AY76)/(1+(AF109+메인!$A$97/10000)/2*AF93/AF94)</f>
+        <f>SUM(AY15:AY76)/(1+(AF8+메인!$A$97/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17600,7 +17621,7 @@
         </is>
       </c>
       <c r="B117" s="24">
-        <f>SUM(V15:V76)/(1+(B109+메인!$A$98/10000)/2*B93/B94)</f>
+        <f>SUM(V15:V76)/(1+(B8+메인!$A$98/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE117" s="5" t="inlineStr">
@@ -17609,7 +17630,7 @@
         </is>
       </c>
       <c r="AF117" s="24">
-        <f>SUM(AZ15:AZ76)/(1+(AF109+메인!$A$98/10000)/2*AF93/AF94)</f>
+        <f>SUM(AZ15:AZ76)/(1+(AF8+메인!$A$98/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17620,7 +17641,7 @@
         </is>
       </c>
       <c r="B118" s="24">
-        <f>SUM(W15:W76)/(1+(B109+메인!$A$99/10000)/2*B93/B94)</f>
+        <f>SUM(W15:W76)/(1+(B8+메인!$A$99/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE118" s="5" t="inlineStr">
@@ -17629,7 +17650,7 @@
         </is>
       </c>
       <c r="AF118" s="24">
-        <f>SUM(BA15:BA76)/(1+(AF109+메인!$A$99/10000)/2*AF93/AF94)</f>
+        <f>SUM(BA15:BA76)/(1+(AF8+메인!$A$99/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17640,7 +17661,7 @@
         </is>
       </c>
       <c r="B119" s="24">
-        <f>SUM(X15:X76)/(1+(B109+메인!$A$100/10000)/2*B93/B94)</f>
+        <f>SUM(X15:X76)/(1+(B8+메인!$A$100/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE119" s="5" t="inlineStr">
@@ -17649,7 +17670,7 @@
         </is>
       </c>
       <c r="AF119" s="24">
-        <f>SUM(BB15:BB76)/(1+(AF109+메인!$A$100/10000)/2*AF93/AF94)</f>
+        <f>SUM(BB15:BB76)/(1+(AF8+메인!$A$100/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17660,7 +17681,7 @@
         </is>
       </c>
       <c r="B120" s="24">
-        <f>SUM(Y15:Y76)/(1+(B109+메인!$A$101/10000)/2*B93/B94)</f>
+        <f>SUM(Y15:Y76)/(1+(B8+메인!$A$101/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE120" s="5" t="inlineStr">
@@ -17669,7 +17690,7 @@
         </is>
       </c>
       <c r="AF120" s="24">
-        <f>SUM(BC15:BC76)/(1+(AF109+메인!$A$101/10000)/2*AF93/AF94)</f>
+        <f>SUM(BC15:BC76)/(1+(AF8+메인!$A$101/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17680,7 +17701,7 @@
         </is>
       </c>
       <c r="B121" s="24">
-        <f>SUM(Z15:Z76)/(1+(B109+메인!$A$102/10000)/2*B93/B94)</f>
+        <f>SUM(Z15:Z76)/(1+(B8+메인!$A$102/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE121" s="5" t="inlineStr">
@@ -17689,7 +17710,7 @@
         </is>
       </c>
       <c r="AF121" s="24">
-        <f>SUM(BD15:BD76)/(1+(AF109+메인!$A$102/10000)/2*AF93/AF94)</f>
+        <f>SUM(BD15:BD76)/(1+(AF8+메인!$A$102/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17700,7 +17721,7 @@
         </is>
       </c>
       <c r="B122" s="24">
-        <f>SUM(AA15:AA76)/(1+(B109+메인!$A$103/10000)/2*B93/B94)</f>
+        <f>SUM(AA15:AA76)/(1+(B8+메인!$A$103/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE122" s="5" t="inlineStr">
@@ -17709,7 +17730,7 @@
         </is>
       </c>
       <c r="AF122" s="24">
-        <f>SUM(BE15:BE76)/(1+(AF109+메인!$A$103/10000)/2*AF93/AF94)</f>
+        <f>SUM(BE15:BE76)/(1+(AF8+메인!$A$103/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
@@ -17720,7 +17741,7 @@
         </is>
       </c>
       <c r="B123" s="24">
-        <f>SUM(AB15:AB76)/(1+(B109+메인!$A$104/10000)/2*B93/B94)</f>
+        <f>SUM(AB15:AB76)/(1+(B8+메인!$A$104/10000)/2*B93/B94)</f>
         <v/>
       </c>
       <c r="AE123" s="5" t="inlineStr">
@@ -17729,7 +17750,7 @@
         </is>
       </c>
       <c r="AF123" s="24">
-        <f>SUM(BF15:BF76)/(1+(AF109+메인!$A$104/10000)/2*AF93/AF94)</f>
+        <f>SUM(BF15:BF76)/(1+(AF8+메인!$A$104/10000)/2*AF93/AF94)</f>
         <v/>
       </c>
     </row>
